--- a/tests/fixtures/formulas.xlsx
+++ b/tests/fixtures/formulas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\New_Office\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDA0EC41-0EAE-4516-8485-FDAB6F23CF3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7BFB87DF-FBD7-4F93-A5F8-E05CED459066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{6A604E93-8407-4FAF-9639-2AFEDF4C26BC}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{A190E3AF-7C41-421C-880B-C64AC6455259}"/>
   </bookViews>
   <sheets>
     <sheet name="Данные" sheetId="1" r:id="rId1"/>
@@ -1257,7 +1257,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;₽&quot;;[Red]\-#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="164" formatCode="\d\d/\m\m/\y\y\y\y"/>
+    <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -1611,11 +1611,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC8D6BF2-1B76-4B31-95ED-D81EE90A36C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAF4BA16-234D-4D9F-9E3D-73FECC539606}">
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1909,7 +1909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61DB7F7B-5EC6-48B4-93D0-ADC8EC0BCA13}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{396A5A25-B47C-45F1-AF97-FF859B68BD27}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1929,7 +1929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD475A9A-4E39-4B26-8323-44C20B9264D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AFCEE06-8B43-486A-8169-4A15DAE01FB3}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1949,7 +1949,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB59DBC0-ADB7-424F-82E9-1F0D08175D1F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A436B245-BB02-42FC-AA89-74DDF81DF596}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1969,7 +1969,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{982B34A7-5EA1-4400-BD1A-EFE2E4E64E6D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9CEFDAA-5BFA-42AF-B256-C09AA09F86EC}">
   <dimension ref="A1:D352"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="C350" s="7">
         <f ca="1">NOW()</f>
-        <v>46305.76681296296</v>
+        <v>46305.785412500001</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C351">
         <f ca="1">RAND()</f>
-        <v>0.54130052384421046</v>
+        <v>0.45911951382031291</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="C352">
         <f ca="1">RANDBETWEEN(1,10)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/tests/fixtures/formulas.xlsx
+++ b/tests/fixtures/formulas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\New_Office\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7BFB87DF-FBD7-4F93-A5F8-E05CED459066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{68F3899C-8939-4350-A78A-B4B6D4C89C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{A190E3AF-7C41-421C-880B-C64AC6455259}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{83716F97-B36F-4C15-8767-04180CEFFDC8}"/>
   </bookViews>
   <sheets>
     <sheet name="Данные" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="403">
   <si>
     <t>Имя</t>
   </si>
@@ -793,6 +793,30 @@
   </si>
   <si>
     <t>TEXTJOIN(";",TRUE,UNIQUE(Данные!B2:B11))</t>
+  </si>
+  <si>
+    <t>SUM({1,2;3,4})</t>
+  </si>
+  <si>
+    <t>INDEX({1,2;3,4}*10,2,2)</t>
+  </si>
+  <si>
+    <t>SUM(-{1,2,3})</t>
+  </si>
+  <si>
+    <t>COUNT(IF(Данные!C2:C11&gt;500,1,""))</t>
+  </si>
+  <si>
+    <t>SUM(IFERROR(1/(Данные!E2:E11-3),0))</t>
+  </si>
+  <si>
+    <t>ROWS(SEQUENCE(5,2))</t>
+  </si>
+  <si>
+    <t>COLUMNS(Данные!A1:H1)</t>
+  </si>
+  <si>
+    <t>SUM(LEN(Данные!A2:A11))</t>
   </si>
   <si>
     <t>LEN(Данные!H2)</t>
@@ -1611,7 +1635,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAF4BA16-234D-4D9F-9E3D-73FECC539606}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27397504-D3DC-4F20-9CDF-EA9E41E7A742}">
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1909,7 +1933,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{396A5A25-B47C-45F1-AF97-FF859B68BD27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36C4F069-F9EE-4AE3-B874-455B9F904C72}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1929,7 +1953,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AFCEE06-8B43-486A-8169-4A15DAE01FB3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{708CEB39-F41C-4F50-B7F8-9EF980C633D4}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1949,7 +1973,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A436B245-BB02-42FC-AA89-74DDF81DF596}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88003679-3863-4D04-9791-941930918051}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1969,8 +1993,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9CEFDAA-5BFA-42AF-B256-C09AA09F86EC}">
-  <dimension ref="A1:D352"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF95873-63AF-4464-A329-68311F176E1D}">
+  <dimension ref="A1:D360"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.140625" style="1"/>
@@ -4436,98 +4460,98 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>7</v>
+        <v>230</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>243</v>
       </c>
       <c r="C206">
-        <f>LEN(Данные!H2)</f>
-        <v>15</v>
+        <f>SUM({1,2;3,4})</f>
+        <v>10</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>7</v>
+        <v>230</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C207" t="str">
-        <f>TRIM(Данные!H2)</f>
-        <v>Привет мир</v>
+      <c r="C207" cm="1">
+        <f t="array" ref="C207">INDEX({1,2;3,4}*10,2,2)</f>
+        <v>40</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>7</v>
+        <v>230</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C208" t="str">
-        <f>UPPER(Данные!H3)</f>
-        <v>ABC</v>
+      <c r="C208" cm="1">
+        <f t="array" ref="C208">SUM(-{1,2,3})</f>
+        <v>-6</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>7</v>
+        <v>230</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C209" t="str">
-        <f>LOWER("ПрИвЕт")</f>
-        <v>привет</v>
+      <c r="C209" cm="1">
+        <f t="array" ref="C209">COUNT(IF(Данные!C2:C11&gt;500,1,""))</f>
+        <v>6</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>7</v>
+        <v>230</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C210" t="str">
-        <f>PROPER("иванов иван")</f>
-        <v>Иванов Иван</v>
+      <c r="C210" cm="1">
+        <f t="array" ref="C210">SUM(IFERROR(1/(Данные!E2:E11-3),0))</f>
+        <v>-0.71666666666666679</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>7</v>
+        <v>230</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C211" t="str">
-        <f>LEFT(Данные!H5,6)</f>
-        <v>Иванов</v>
+      <c r="C211">
+        <f>ROWS(_xlfn.SEQUENCE(5,2))</f>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>7</v>
+        <v>230</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C212" t="str">
-        <f>RIGHT(Данные!H4,3)</f>
-        <v>123</v>
+      <c r="C212">
+        <f>COLUMNS(Данные!A1:H1)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>7</v>
+        <v>230</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C213" t="str">
-        <f>MID(Данные!H5,8,4)</f>
-        <v>Иван</v>
+      <c r="C213" cm="1">
+        <f t="array" ref="C213">SUM(LEN(Данные!A2:A11))</f>
+        <v>43</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4537,9 +4561,9 @@
       <c r="B214" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="C214" t="str">
-        <f>LEFT("abc")</f>
-        <v>a</v>
+      <c r="C214">
+        <f>LEN(Данные!H2)</f>
+        <v>15</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4549,9 +4573,9 @@
       <c r="B215" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C215">
-        <f>FIND("-",Данные!H4)</f>
-        <v>4</v>
+      <c r="C215" t="str">
+        <f>TRIM(Данные!H2)</f>
+        <v>Привет мир</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4561,9 +4585,9 @@
       <c r="B216" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C216" t="e">
-        <f>FIND("z","abc")</f>
-        <v>#VALUE!</v>
+      <c r="C216" t="str">
+        <f>UPPER(Данные!H3)</f>
+        <v>ABC</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4573,9 +4597,9 @@
       <c r="B217" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C217">
-        <f>SEARCH("иван",Данные!H5)</f>
-        <v>1</v>
+      <c r="C217" t="str">
+        <f>LOWER("ПрИвЕт")</f>
+        <v>привет</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4585,9 +4609,9 @@
       <c r="B218" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C218">
-        <f>SEARCH("?ва",Данные!H5)</f>
-        <v>1</v>
+      <c r="C218" t="str">
+        <f>PROPER("иванов иван")</f>
+        <v>Иванов Иван</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4598,8 +4622,8 @@
         <v>256</v>
       </c>
       <c r="C219" t="str">
-        <f>SUBSTITUTE(Данные!H6,",",";")</f>
-        <v>a;b;c</v>
+        <f>LEFT(Данные!H5,6)</f>
+        <v>Иванов</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4610,8 +4634,8 @@
         <v>257</v>
       </c>
       <c r="C220" t="str">
-        <f>SUBSTITUTE("a-a-a","a","b",2)</f>
-        <v>a-b-a</v>
+        <f>RIGHT(Данные!H4,3)</f>
+        <v>123</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4622,8 +4646,8 @@
         <v>258</v>
       </c>
       <c r="C221" t="str">
-        <f>REPLACE("abcdef",2,3,"X")</f>
-        <v>aXef</v>
+        <f>MID(Данные!H5,8,4)</f>
+        <v>Иван</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4634,8 +4658,8 @@
         <v>259</v>
       </c>
       <c r="C222" t="str">
-        <f>REPT("ab",3)</f>
-        <v>ababab</v>
+        <f>LEFT("abc")</f>
+        <v>a</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4645,9 +4669,9 @@
       <c r="B223" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C223" t="str">
-        <f>CONCATENATE("a",1,TRUE)</f>
-        <v>a1ИСТИНА</v>
+      <c r="C223">
+        <f>FIND("-",Данные!H4)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4657,9 +4681,9 @@
       <c r="B224" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C224" t="str">
-        <f>_xlfn.CONCAT(Данные!A2:A4)</f>
-        <v>ИванПётрМария</v>
+      <c r="C224" t="e">
+        <f>FIND("z","abc")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4669,9 +4693,9 @@
       <c r="B225" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C225" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,Данные!A2:A5)</f>
-        <v>Иван, Пётр, Мария, Анна</v>
+      <c r="C225">
+        <f>SEARCH("иван",Данные!H5)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4681,9 +4705,9 @@
       <c r="B226" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C226" t="str">
-        <f>_xlfn.TEXTJOIN("-",FALSE,"a","","b")</f>
-        <v>a--b</v>
+      <c r="C226">
+        <f>SEARCH("?ва",Данные!H5)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4693,9 +4717,9 @@
       <c r="B227" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C227" t="b">
-        <f>EXACT("abc","ABC")</f>
-        <v>0</v>
+      <c r="C227" t="str">
+        <f>SUBSTITUTE(Данные!H6,",",";")</f>
+        <v>a;b;c</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4706,8 +4730,8 @@
         <v>265</v>
       </c>
       <c r="C228" t="str">
-        <f>CHAR(65)</f>
-        <v>A</v>
+        <f>SUBSTITUTE("a-a-a","a","b",2)</f>
+        <v>a-b-a</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4717,9 +4741,9 @@
       <c r="B229" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C229">
-        <f>CODE("A")</f>
-        <v>65</v>
+      <c r="C229" t="str">
+        <f>REPLACE("abcdef",2,3,"X")</f>
+        <v>aXef</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4730,8 +4754,8 @@
         <v>267</v>
       </c>
       <c r="C230" t="str">
-        <f>_xlfn.UNICHAR(1046)</f>
-        <v>Ж</v>
+        <f>REPT("ab",3)</f>
+        <v>ababab</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4741,9 +4765,9 @@
       <c r="B231" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C231">
-        <f>_xlfn.UNICODE("Ж")</f>
-        <v>1046</v>
+      <c r="C231" t="str">
+        <f>CONCATENATE("a",1,TRUE)</f>
+        <v>a1ИСТИНА</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4754,8 +4778,8 @@
         <v>269</v>
       </c>
       <c r="C232" t="str">
-        <f>CLEAN("a"&amp;CHAR(10)&amp;"b")</f>
-        <v>ab</v>
+        <f>_xlfn.CONCAT(Данные!A2:A4)</f>
+        <v>ИванПётрМария</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4765,9 +4789,9 @@
       <c r="B233" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C233">
-        <f>VALUE("1 234,5")</f>
-        <v>1234.5</v>
+      <c r="C233" t="str">
+        <f>_xlfn.TEXTJOIN(", ",TRUE,Данные!A2:A5)</f>
+        <v>Иван, Пётр, Мария, Анна</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4777,9 +4801,9 @@
       <c r="B234" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C234">
-        <f>VALUE("12%")</f>
-        <v>0.12</v>
+      <c r="C234" t="str">
+        <f>_xlfn.TEXTJOIN("-",FALSE,"a","","b")</f>
+        <v>a--b</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4789,9 +4813,9 @@
       <c r="B235" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C235" t="e">
-        <f>VALUE("abc")</f>
-        <v>#VALUE!</v>
+      <c r="C235" t="b">
+        <f>EXACT("abc","ABC")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4801,9 +4825,9 @@
       <c r="B236" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="C236">
-        <f>_xlfn.NUMBERVALUE("1.234,5",",",".")</f>
-        <v>1234.5</v>
+      <c r="C236" t="str">
+        <f>CHAR(65)</f>
+        <v>A</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4813,9 +4837,9 @@
       <c r="B237" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C237" t="str">
-        <f>T(Данные!H3)</f>
-        <v>abc</v>
+      <c r="C237">
+        <f>CODE("A")</f>
+        <v>65</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4826,8 +4850,8 @@
         <v>275</v>
       </c>
       <c r="C238" t="str">
-        <f>T(5)</f>
-        <v/>
+        <f>_xlfn.UNICHAR(1046)</f>
+        <v>Ж</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4837,9 +4861,9 @@
       <c r="B239" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C239" t="e">
-        <f>TEXT(1234.567,"0.00")</f>
-        <v>#VALUE!</v>
+      <c r="C239">
+        <f>_xlfn.UNICODE("Ж")</f>
+        <v>1046</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -4850,8 +4874,8 @@
         <v>277</v>
       </c>
       <c r="C240" t="str">
-        <f>TEXT(1234.567,"# ##0,00")</f>
-        <v>1 234,57</v>
+        <f>CLEAN("a"&amp;CHAR(10)&amp;"b")</f>
+        <v>ab</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -4861,9 +4885,9 @@
       <c r="B241" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C241" t="str">
-        <f>TEXT(0.256,"0%")</f>
-        <v>26%</v>
+      <c r="C241">
+        <f>VALUE("1 234,5")</f>
+        <v>1234.5</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -4873,9 +4897,9 @@
       <c r="B242" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C242" t="str">
-        <f>TEXT(46301,"ДД.ММ.ГГГГ")</f>
-        <v>06.10.2026</v>
+      <c r="C242">
+        <f>VALUE("12%")</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -4885,9 +4909,9 @@
       <c r="B243" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="C243" t="str">
-        <f>TEXT(46301,"dd.mm.yyyy")</f>
-        <v>dd.mm.yyyy</v>
+      <c r="C243" t="e">
+        <f>VALUE("abc")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -4897,9 +4921,9 @@
       <c r="B244" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C244" t="str">
-        <f>TEXT(46301,"ДДДД")</f>
-        <v>вторник</v>
+      <c r="C244">
+        <f>_xlfn.NUMBERVALUE("1.234,5",",",".")</f>
+        <v>1234.5</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -4910,8 +4934,8 @@
         <v>282</v>
       </c>
       <c r="C245" t="str">
-        <f>TEXT(46301,"ММММ ГГГГ")</f>
-        <v>Октябрь 2026</v>
+        <f>T(Данные!H3)</f>
+        <v>abc</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -4922,8 +4946,8 @@
         <v>283</v>
       </c>
       <c r="C246" t="str">
-        <f>FIXED(1234.567,1)</f>
-        <v>1 234,6</v>
+        <f>T(5)</f>
+        <v/>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -4933,9 +4957,9 @@
       <c r="B247" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C247" t="str">
-        <f>DOLLAR(1234.5)</f>
-        <v>1 234,50 ₽</v>
+      <c r="C247" t="e">
+        <f>TEXT(1234.567,"0.00")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -4945,9 +4969,9 @@
       <c r="B248" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C248" t="e" cm="1">
-        <f t="array" aca="1" ref="C248" ca="1">TEXTBEFORE(Данные!H8,":")</f>
-        <v>#NAME?</v>
+      <c r="C248" t="str">
+        <f>TEXT(1234.567,"# ##0,00")</f>
+        <v>1 234,57</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -4957,9 +4981,9 @@
       <c r="B249" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C249" t="e" cm="1">
-        <f t="array" aca="1" ref="C249" ca="1">TEXTAFTER(Данные!H8,": ")</f>
-        <v>#NAME?</v>
+      <c r="C249" t="str">
+        <f>TEXT(0.256,"0%")</f>
+        <v>26%</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -4969,9 +4993,9 @@
       <c r="B250" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="C250" t="e" cm="1">
-        <f t="array" aca="1" ref="C250" ca="1">INDEX(TEXTSPLIT(Данные!H6,","),2)</f>
-        <v>#NAME?</v>
+      <c r="C250" t="str">
+        <f>TEXT(46301,"ДД.ММ.ГГГГ")</f>
+        <v>06.10.2026</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -4981,9 +5005,9 @@
       <c r="B251" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C251">
-        <f>LEN(Данные!H5)-LEN(SUBSTITUTE(Данные!H5," ",""))+1</f>
-        <v>3</v>
+      <c r="C251" t="str">
+        <f>TEXT(46301,"dd.mm.yyyy")</f>
+        <v>dd.mm.yyyy</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -4994,1208 +5018,1304 @@
         <v>289</v>
       </c>
       <c r="C252" t="str">
+        <f>TEXT(46301,"ДДДД")</f>
+        <v>вторник</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>7</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C253" t="str">
+        <f>TEXT(46301,"ММММ ГГГГ")</f>
+        <v>Октябрь 2026</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>7</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C254" t="str">
+        <f>FIXED(1234.567,1)</f>
+        <v>1 234,6</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>7</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C255" t="str">
+        <f>DOLLAR(1234.5)</f>
+        <v>1 234,50 ₽</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>7</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C256" t="e" cm="1">
+        <f t="array" aca="1" ref="C256" ca="1">TEXTBEFORE(Данные!H8,":")</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>7</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C257" t="e" cm="1">
+        <f t="array" aca="1" ref="C257" ca="1">TEXTAFTER(Данные!H8,": ")</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>7</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C258" t="e" cm="1">
+        <f t="array" aca="1" ref="C258" ca="1">INDEX(TEXTSPLIT(Данные!H6,","),2)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>7</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C259">
+        <f>LEN(Данные!H5)-LEN(SUBSTITUTE(Данные!H5," ",""))+1</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>7</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C260" t="str">
         <f>Данные!A2&amp;" ("&amp;Данные!B2&amp;")"</f>
         <v>Иван (Продажи)</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
-        <v>290</v>
-      </c>
-      <c r="B253" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C253" s="3">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>298</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C261" s="3">
         <f>DATE(2026,10,10)</f>
         <v>46305</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
-        <v>290</v>
-      </c>
-      <c r="B254" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C254" s="3">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>298</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C262" s="3">
         <f>DATE(2026,13,1)</f>
         <v>46388</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>290</v>
-      </c>
-      <c r="B255" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="C255" s="3">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>298</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C263" s="3">
         <f>DATE(2026,1,0)</f>
         <v>46022</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>290</v>
-      </c>
-      <c r="B256" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="C256" s="3">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>298</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C264" s="3">
         <f>DATE(26,1,1)</f>
         <v>9498</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
-        <v>290</v>
-      </c>
-      <c r="B257" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="C257">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>298</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C265">
         <f>YEAR(Данные!D2)</f>
         <v>2026</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A258" t="s">
-        <v>290</v>
-      </c>
-      <c r="B258" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C258">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>298</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C266">
         <f>MONTH(Данные!D3)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A259" t="s">
-        <v>290</v>
-      </c>
-      <c r="B259" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="C259">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>298</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C267">
         <f>DAY(Данные!D6)</f>
         <v>29</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A260" t="s">
-        <v>290</v>
-      </c>
-      <c r="B260" s="1" t="s">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
         <v>298</v>
       </c>
-      <c r="C260" s="3">
+      <c r="B268" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C268" s="3">
         <f>DATE(1900,2,29)</f>
         <v>60</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
-        <v>290</v>
-      </c>
-      <c r="B261" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C261" s="3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>298</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C269" s="3">
         <f>DATE(1900,3,1)</f>
         <v>61</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
-        <v>290</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C262">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>298</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C270">
         <f>WEEKDAY(Данные!D2)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
-        <v>290</v>
-      </c>
-      <c r="B263" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C263">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>298</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C271">
         <f>WEEKDAY(Данные!D2,2)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A264" t="s">
-        <v>290</v>
-      </c>
-      <c r="B264" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="C264">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>298</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C272">
         <f>WEEKNUM(Данные!D2,2)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
-        <v>290</v>
-      </c>
-      <c r="B265" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C265">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>298</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C273">
         <f>_xlfn.ISOWEEKNUM(Данные!D2)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
-        <v>290</v>
-      </c>
-      <c r="B266" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C266">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>298</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C274">
         <f>EDATE(Данные!D2,1)</f>
         <v>46068</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A267" t="s">
-        <v>290</v>
-      </c>
-      <c r="B267" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C267">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>298</v>
+      </c>
+      <c r="B275" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C275">
         <f>EDATE(DATE(2026,1,31),1)</f>
         <v>46081</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A268" t="s">
-        <v>290</v>
-      </c>
-      <c r="B268" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C268">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>298</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C276">
         <f>EOMONTH(Данные!D2,0)</f>
         <v>46053</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A269" t="s">
-        <v>290</v>
-      </c>
-      <c r="B269" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C269">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>298</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C277">
         <f>EOMONTH(Данные!D2,-1)</f>
         <v>46022</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A270" t="s">
-        <v>290</v>
-      </c>
-      <c r="B270" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="C270">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>298</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C278">
         <f>WORKDAY(Данные!D2,10)</f>
         <v>46051</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A271" t="s">
-        <v>290</v>
-      </c>
-      <c r="B271" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="C271">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>298</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C279">
         <f>WORKDAY.INTL(Данные!D2,10,11)</f>
         <v>46049</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A272" t="s">
-        <v>290</v>
-      </c>
-      <c r="B272" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C272">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>298</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C280">
         <f>NETWORKDAYS(Данные!D2,Данные!D3)</f>
         <v>32</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
-        <v>290</v>
-      </c>
-      <c r="B273" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="C273">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>298</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C281">
         <f>NETWORKDAYS.INTL(Данные!D2,Данные!D3,1)</f>
         <v>32</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A274" t="s">
-        <v>290</v>
-      </c>
-      <c r="B274" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="C274">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>298</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C282">
         <f>DATEDIF(Данные!D6,Данные!D2,"y")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A275" t="s">
-        <v>290</v>
-      </c>
-      <c r="B275" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C275">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>298</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C283">
         <f>DATEDIF(Данные!D6,Данные!D2,"m")</f>
         <v>22</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
-        <v>290</v>
-      </c>
-      <c r="B276" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="C276">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>298</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C284">
         <f>DATEDIF(Данные!D6,Данные!D2,"md")</f>
         <v>17</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
-        <v>290</v>
-      </c>
-      <c r="B277" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="C277">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>298</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C285">
         <f>_xlfn.DAYS(Данные!D3,Данные!D2)</f>
         <v>44</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A278" t="s">
-        <v>290</v>
-      </c>
-      <c r="B278" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C278">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>298</v>
+      </c>
+      <c r="B286" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C286">
         <f>Данные!D3-Данные!D2</f>
         <v>44</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A279" t="s">
-        <v>290</v>
-      </c>
-      <c r="B279" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="C279">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>298</v>
+      </c>
+      <c r="B287" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C287">
         <f>YEARFRAC(Данные!D2,Данные!D3)</f>
         <v>0.11944444444444445</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A280" t="s">
-        <v>290</v>
-      </c>
-      <c r="B280" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C280">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>298</v>
+      </c>
+      <c r="B288" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C288">
         <f>YEARFRAC(Данные!D2,Данные!D3,1)</f>
         <v>0.12054794520547946</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A281" t="s">
-        <v>290</v>
-      </c>
-      <c r="B281" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C281">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>298</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C289">
         <f>DAYS360(Данные!D2,Данные!D3)</f>
         <v>43</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A282" t="s">
-        <v>290</v>
-      </c>
-      <c r="B282" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C282" s="4">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>298</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C290" s="4">
         <f>TIME(14,30,0)</f>
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A283" t="s">
-        <v>290</v>
-      </c>
-      <c r="B283" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C283">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>298</v>
+      </c>
+      <c r="B291" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C291">
         <f>HOUR(0.75)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A284" t="s">
-        <v>290</v>
-      </c>
-      <c r="B284" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C284">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>298</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C292">
         <f>MINUTE(TIME(14,30,15))</f>
         <v>30</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A285" t="s">
-        <v>290</v>
-      </c>
-      <c r="B285" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C285">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>298</v>
+      </c>
+      <c r="B293" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C293">
         <f>SECOND(TIME(14,30,15))</f>
         <v>15</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A286" t="s">
-        <v>290</v>
-      </c>
-      <c r="B286" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="C286">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>298</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C294">
         <f>DATEVALUE("15.01.2026")</f>
         <v>46037</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A287" t="s">
-        <v>290</v>
-      </c>
-      <c r="B287" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="C287">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>298</v>
+      </c>
+      <c r="B295" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C295">
         <f>TIMEVALUE("14:30")</f>
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A288" t="s">
-        <v>290</v>
-      </c>
-      <c r="B288" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="C288">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>298</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C296">
         <f>Данные!D2+30</f>
         <v>46067</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A289" t="s">
-        <v>327</v>
-      </c>
-      <c r="B289" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C289" t="e">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>335</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C297" t="e">
         <f>AVERAGEA(Данные!G2:G11)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A290" t="s">
-        <v>327</v>
-      </c>
-      <c r="B290" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="C290">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>335</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C298">
         <f>MAXA(Данные!F2:F11)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A291" t="s">
-        <v>327</v>
-      </c>
-      <c r="B291" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C291">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>335</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C299">
         <f>MINA(Данные!F2:F11)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A292" t="s">
-        <v>327</v>
-      </c>
-      <c r="B292" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C292">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>335</v>
+      </c>
+      <c r="B300" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C300">
         <f>LARGE(Данные!C2:C11,2)</f>
         <v>3100</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A293" t="s">
-        <v>327</v>
-      </c>
-      <c r="B293" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="C293">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>335</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C301">
         <f>SMALL(Данные!C2:C11,3)</f>
         <v>15.25</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A294" t="s">
-        <v>327</v>
-      </c>
-      <c r="B294" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="C294">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>335</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C302">
         <f>MODE(Данные!E2:E11)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A295" t="s">
-        <v>327</v>
-      </c>
-      <c r="B295" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="C295">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>335</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C303">
         <f>_xlfn.MODE.SNGL(Данные!E2:E11)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
-        <v>327</v>
-      </c>
-      <c r="B296" s="1" t="s">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
         <v>335</v>
       </c>
-      <c r="C296">
+      <c r="B304" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C304">
         <f>STDEV(Данные!C2:C11)</f>
         <v>1440.7163536954647</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
-        <v>327</v>
-      </c>
-      <c r="B297" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C297">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>335</v>
+      </c>
+      <c r="B305" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C305">
         <f>_xlfn.STDEV.S(Данные!C2:C11)</f>
         <v>1440.7163536954647</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A298" t="s">
-        <v>327</v>
-      </c>
-      <c r="B298" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="C298">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>335</v>
+      </c>
+      <c r="B306" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C306">
         <f>_xlfn.STDEV.P(Данные!C2:C11)</f>
         <v>1366.783541979124</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A299" t="s">
-        <v>327</v>
-      </c>
-      <c r="B299" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="C299">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>335</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C307">
         <f>STDEVP(Данные!C2:C11)</f>
         <v>1366.783541979124</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A300" t="s">
-        <v>327</v>
-      </c>
-      <c r="B300" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="C300">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>335</v>
+      </c>
+      <c r="B308" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C308">
         <f>VAR(Данные!C2:C11)</f>
         <v>2075663.6118055556</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A301" t="s">
-        <v>327</v>
-      </c>
-      <c r="B301" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="C301">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>335</v>
+      </c>
+      <c r="B309" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C309">
         <f>_xlfn.VAR.P(Данные!C2:C11)</f>
         <v>1868097.2506250001</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A302" t="s">
-        <v>327</v>
-      </c>
-      <c r="B302" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C302">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>335</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C310">
         <f>QUARTILE(Данные!C2:C11,1)</f>
         <v>69.0625</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
-        <v>327</v>
-      </c>
-      <c r="B303" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="C303">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>335</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C311">
         <f>_xlfn.QUARTILE.EXC(Данные!C2:C11,1)</f>
         <v>11.4375</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A304" t="s">
-        <v>327</v>
-      </c>
-      <c r="B304" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="C304">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>335</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C312">
         <f>PERCENTILE(Данные!C2:C11,0.9)</f>
         <v>3209.9999999999995</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
-        <v>327</v>
-      </c>
-      <c r="B305" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C305">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>335</v>
+      </c>
+      <c r="B313" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C313">
         <f>_xlfn.PERCENTILE.EXC(Данные!C2:C11,0.9)</f>
         <v>4090.0000000000005</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
-        <v>327</v>
-      </c>
-      <c r="B306" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C306">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>335</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C314">
         <f>PERCENTRANK(Данные!C2:C11,980)</f>
         <v>0.55500000000000005</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
-        <v>327</v>
-      </c>
-      <c r="B307" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C307">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>335</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C315">
         <f>CORREL(Данные!C2:C11,Данные!E2:E11)</f>
         <v>-0.50890990310890893</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
-        <v>327</v>
-      </c>
-      <c r="B308" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="C308">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>335</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C316">
         <f>SLOPE(Данные!C2:C11,Данные!E2:E11)</f>
         <v>-291.59797891036908</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A309" t="s">
-        <v>327</v>
-      </c>
-      <c r="B309" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C309">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>335</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C317">
         <f>INTERCEPT(Данные!C2:C11,Данные!E2:E11)</f>
         <v>2315.8071177504394</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A310" t="s">
-        <v>327</v>
-      </c>
-      <c r="B310" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="C310">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>335</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C318">
         <f>FORECAST(10,Данные!C2:C11,Данные!E2:E11)</f>
         <v>-600.17267135325119</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A311" t="s">
-        <v>327</v>
-      </c>
-      <c r="B311" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C311">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>335</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C319">
         <f>_xlfn.FORECAST.LINEAR(10,Данные!C2:C11,Данные!E2:E11)</f>
         <v>-600.17267135325119</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A312" t="s">
-        <v>327</v>
-      </c>
-      <c r="B312" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="C312" cm="1">
-        <f t="array" ref="C312">INDEX(TREND(Данные!C2:C11,Данные!E2:E11),1)</f>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>335</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C320" cm="1">
+        <f t="array" ref="C320">INDEX(TREND(Данные!C2:C11,Данные!E2:E11),1)</f>
         <v>1441.0131810193325</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A313" t="s">
-        <v>327</v>
-      </c>
-      <c r="B313" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C313" cm="1">
-        <f t="array" ref="C313">INDEX(FREQUENCY(Данные!C2:C11,{0,1000,3000}),2)</f>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>335</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C321" cm="1">
+        <f t="array" ref="C321">INDEX(FREQUENCY(Данные!C2:C11,{0,1000,3000}),2)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
-        <v>327</v>
-      </c>
-      <c r="B314" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C314">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>335</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C322">
         <f>GEOMEAN(Данные!E2:E11)</f>
         <v>3.0949600815477374</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A315" t="s">
-        <v>327</v>
-      </c>
-      <c r="B315" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="C315">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>335</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C323">
         <f>HARMEAN(Данные!E2:E11)</f>
         <v>2.3708721422523285</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
-        <v>327</v>
-      </c>
-      <c r="B316" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="C316">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>335</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C324">
         <f>AVEDEV(Данные!C2:C11)</f>
         <v>1057.1399999999999</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A317" t="s">
-        <v>327</v>
-      </c>
-      <c r="B317" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C317">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>335</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C325">
         <f>DEVSQ(Данные!C2:C11)</f>
         <v>18680972.506250005</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A318" t="s">
-        <v>327</v>
-      </c>
-      <c r="B318" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="C318">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>335</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C326">
         <f>COUNTA(Данные!A:A)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A319" t="s">
-        <v>327</v>
-      </c>
-      <c r="B319" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C319">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>335</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C327">
         <f>_xlfn.NORM.DIST(1,0,1,TRUE)</f>
         <v>0.84134474606854304</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A320" t="s">
-        <v>327</v>
-      </c>
-      <c r="B320" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C320">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>335</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C328">
         <f>_xlfn.NORM.INV(0.95,0,1)</f>
         <v>1.6448536269514715</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A321" t="s">
-        <v>327</v>
-      </c>
-      <c r="B321" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C321">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>335</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C329">
         <f>_xlfn.NORM.S.DIST(1.96,TRUE)</f>
         <v>0.97500210485177952</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A322" t="s">
-        <v>361</v>
-      </c>
-      <c r="B322" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="C322" s="5">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>369</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C330" s="5">
         <f>PMT(0.1/12,36,-100000)</f>
         <v>3226.7187193837485</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A323" t="s">
-        <v>361</v>
-      </c>
-      <c r="B323" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="C323" s="5">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>369</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C331" s="5">
         <f>PMT(0.08,10,10000,0,1)</f>
         <v>-1379.9026731210683</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A324" t="s">
-        <v>361</v>
-      </c>
-      <c r="B324" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="C324" s="5">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>369</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C332" s="5">
         <f>IPMT(0.1/12,1,36,-100000)</f>
         <v>833.33333333333337</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A325" t="s">
-        <v>361</v>
-      </c>
-      <c r="B325" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="C325" s="5">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>369</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C333" s="5">
         <f>PPMT(0.1/12,1,36,-100000)</f>
         <v>2393.3853860504155</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A326" t="s">
-        <v>361</v>
-      </c>
-      <c r="B326" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="C326" s="5">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>369</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C334" s="5">
         <f>FV(0.05,10,-100)</f>
         <v>1257.7892535548831</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A327" t="s">
-        <v>361</v>
-      </c>
-      <c r="B327" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="C327" s="5">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>369</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C335" s="5">
         <f>PV(0.05,10,-100)</f>
         <v>772.17349291848132</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A328" t="s">
-        <v>361</v>
-      </c>
-      <c r="B328" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="C328">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>369</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C336">
         <f>NPER(0.01,-100,1000)</f>
         <v>10.588644459423231</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A329" t="s">
-        <v>361</v>
-      </c>
-      <c r="B329" s="1" t="s">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
         <v>369</v>
       </c>
-      <c r="C329" s="6">
+      <c r="B337" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C337" s="6">
         <f>RATE(36,-3000,100000)</f>
         <v>4.2206675453815533E-3</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A330" t="s">
-        <v>361</v>
-      </c>
-      <c r="B330" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="C330" s="5">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>369</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C338" s="5">
         <f>NPV(0.1,-1000,300,400,500)</f>
         <v>-19.12437675022209</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A331" t="s">
-        <v>361</v>
-      </c>
-      <c r="B331" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="C331" s="6">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>369</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C339" s="6">
         <f>IRR({-1000,300,400,500})</f>
         <v>8.8963394693349906E-2</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A332" t="s">
-        <v>361</v>
-      </c>
-      <c r="B332" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="C332">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>369</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C340">
         <f>XNPV(0.1,{-1000,600,600},{46023,46388,46753})</f>
         <v>41.322314049586623</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A333" t="s">
-        <v>361</v>
-      </c>
-      <c r="B333" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C333">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>369</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C341">
         <f>XIRR({-1000,600,600},{46023,46388,46753})</f>
         <v>0.13066238760948182</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A334" t="s">
-        <v>361</v>
-      </c>
-      <c r="B334" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C334" s="5">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>369</v>
+      </c>
+      <c r="B342" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C342" s="5">
         <f>SLN(10000,1000,5)</f>
         <v>1800</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A335" t="s">
-        <v>361</v>
-      </c>
-      <c r="B335" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="C335" s="5">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>369</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C343" s="5">
         <f>DB(10000,1000,5,1)</f>
         <v>3690</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A336" t="s">
-        <v>361</v>
-      </c>
-      <c r="B336" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C336" s="5">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>369</v>
+      </c>
+      <c r="B344" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C344" s="5">
         <f>DDB(10000,1000,5,1)</f>
         <v>4000</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A337" t="s">
-        <v>361</v>
-      </c>
-      <c r="B337" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="C337" s="5">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>369</v>
+      </c>
+      <c r="B345" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C345" s="5">
         <f>SYD(10000,1000,5,1)</f>
         <v>3000</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A338" t="s">
-        <v>361</v>
-      </c>
-      <c r="B338" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="C338">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>369</v>
+      </c>
+      <c r="B346" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C346">
         <f>EFFECT(0.1,12)</f>
         <v>0.10471306744129683</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A339" t="s">
-        <v>361</v>
-      </c>
-      <c r="B339" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="C339">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>369</v>
+      </c>
+      <c r="B347" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C347">
         <f>NOMINAL(0.1047,12)</f>
         <v>9.9988072551626672E-2</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A340" t="s">
-        <v>380</v>
-      </c>
-      <c r="B340" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="C340" t="e">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>388</v>
+      </c>
+      <c r="B348" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C348" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A341" t="s">
-        <v>380</v>
-      </c>
-      <c r="B341" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="C341" t="b">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>388</v>
+      </c>
+      <c r="B349" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C349" t="b">
         <f>ISNA(NA())</f>
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A342" t="s">
-        <v>380</v>
-      </c>
-      <c r="B342" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="C342">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>388</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C350">
         <f>ERROR.TYPE(1/0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A343" t="s">
-        <v>380</v>
-      </c>
-      <c r="B343" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="C343">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>388</v>
+      </c>
+      <c r="B351" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C351">
         <f ca="1">_xlfn.SHEET()</f>
         <v>5</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A344" t="s">
-        <v>380</v>
-      </c>
-      <c r="B344" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="C344">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>388</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C352">
         <f ca="1">_xlfn.SHEETS()</f>
         <v>5</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A345" t="s">
-        <v>380</v>
-      </c>
-      <c r="B345" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="C345" t="str">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>388</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C353" t="str">
         <f ca="1">_xlfn.FORMULATEXT(Данные!G6)</f>
         <v>=НД()</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A346" t="s">
-        <v>380</v>
-      </c>
-      <c r="B346" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="C346" cm="1">
-        <f t="array" aca="1" ref="C346" ca="1">CELL("row",Данные!C5)</f>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>388</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C354" cm="1">
+        <f t="array" aca="1" ref="C354" ca="1">CELL("row",Данные!C5)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A347" t="s">
-        <v>380</v>
-      </c>
-      <c r="B347" s="1" t="s">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
         <v>388</v>
       </c>
-      <c r="C347">
+      <c r="B355" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C355">
         <f>_xlfn.LET(_xlpm.x,5,_xlpm.y,_xlpm.x*2,_xlpm.x+_xlpm.y)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A348" t="s">
-        <v>380</v>
-      </c>
-      <c r="B348" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="C348">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>388</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C356">
         <f>ROWS(Данные!A:A)</f>
         <v>1048576</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A349" t="s">
-        <v>390</v>
-      </c>
-      <c r="B349" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="C349" s="3">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>398</v>
+      </c>
+      <c r="B357" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C357" s="3">
         <f ca="1">TODAY()</f>
         <v>46305</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A350" t="s">
-        <v>390</v>
-      </c>
-      <c r="B350" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="C350" s="7">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>398</v>
+      </c>
+      <c r="B358" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C358" s="7">
         <f ca="1">NOW()</f>
-        <v>46305.785412500001</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A351" t="s">
-        <v>390</v>
-      </c>
-      <c r="B351" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="C351">
+        <v>46305.800251736109</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>398</v>
+      </c>
+      <c r="B359" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C359">
         <f ca="1">RAND()</f>
-        <v>0.45911951382031291</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A352" t="s">
-        <v>390</v>
-      </c>
-      <c r="B352" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="C352">
+        <v>0.46765363586999198</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>398</v>
+      </c>
+      <c r="B360" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C360">
         <f ca="1">RANDBETWEEN(1,10)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/tests/fixtures/formulas.xlsx
+++ b/tests/fixtures/formulas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\New_Office\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2F9185A-FE89-4C07-B05A-488A5E1238A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBDC992A-0119-4403-AEE2-D29DE71248DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7477EA5A-1744-43AA-9759-3D5CDAD530C9}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{2A13D604-5984-403D-890D-D13B94968E51}"/>
   </bookViews>
   <sheets>
     <sheet name="Данные" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1919" uniqueCount="1292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2171" uniqueCount="1461">
   <si>
     <t>Имя</t>
   </si>
@@ -3940,6 +3940,513 @@
   </si>
   <si>
     <t>=ТИП.ОШИБКИ(ДРВ("x";;"y"))</t>
+  </si>
+  <si>
+    <t>Пакет B: распределения и тесты</t>
+  </si>
+  <si>
+    <t>BETA.DIST(0.4,2,3,TRUE)</t>
+  </si>
+  <si>
+    <t>=БЕТА.РАСП(0,4;2;3;ИСТИНА)</t>
+  </si>
+  <si>
+    <t>BETA.DIST(0.4,2,3,FALSE)</t>
+  </si>
+  <si>
+    <t>=БЕТА.РАСП(0,4;2;3;ЛОЖЬ)</t>
+  </si>
+  <si>
+    <t>BETA.DIST(2,8,10,TRUE,1,3)</t>
+  </si>
+  <si>
+    <t>=БЕТА.РАСП(2;8;10;ИСТИНА;1;3)</t>
+  </si>
+  <si>
+    <t>BETADIST(2,8,10,1,3)</t>
+  </si>
+  <si>
+    <t>=БЕТАРАСП(2;8;10;1;3)</t>
+  </si>
+  <si>
+    <t>BETA.INV(0.685470581,8,10,1,3)</t>
+  </si>
+  <si>
+    <t>=БЕТА.ОБР(0,685470581;8;10;1;3)</t>
+  </si>
+  <si>
+    <t>BETAINV(0.2,4,5)</t>
+  </si>
+  <si>
+    <t>=БЕТАОБР(0,2;4;5)</t>
+  </si>
+  <si>
+    <t>BINOM.DIST(6,10,0.5,FALSE)</t>
+  </si>
+  <si>
+    <t>=БИНОМ.РАСП(6;10;0,5;ЛОЖЬ)</t>
+  </si>
+  <si>
+    <t>BINOM.DIST(6,10,0.5,TRUE)</t>
+  </si>
+  <si>
+    <t>=БИНОМ.РАСП(6;10;0,5;ИСТИНА)</t>
+  </si>
+  <si>
+    <t>BINOMDIST(3,8,0.25,TRUE)</t>
+  </si>
+  <si>
+    <t>=БИНОМРАСП(3;8;0,25;ИСТИНА)</t>
+  </si>
+  <si>
+    <t>BINOM.DIST.RANGE(60,0.75,48)</t>
+  </si>
+  <si>
+    <t>=БИНОМ.РАСП.ДИАП(60;0,75;48)</t>
+  </si>
+  <si>
+    <t>BINOM.DIST.RANGE(60,0.75,45,50)</t>
+  </si>
+  <si>
+    <t>=БИНОМ.РАСП.ДИАП(60;0,75;45;50)</t>
+  </si>
+  <si>
+    <t>BINOM.INV(6,0.5,0.75)</t>
+  </si>
+  <si>
+    <t>=БИНОМ.ОБР(6;0,5;0,75)</t>
+  </si>
+  <si>
+    <t>CRITBINOM(10,0.3,0.5)</t>
+  </si>
+  <si>
+    <t>=КРИТБИНОМ(10;0,3;0,5)</t>
+  </si>
+  <si>
+    <t>CHISQ.DIST(0.5,1,TRUE)</t>
+  </si>
+  <si>
+    <t>=ХИ2.РАСП(0,5;1;ИСТИНА)</t>
+  </si>
+  <si>
+    <t>CHISQ.DIST(2,3,FALSE)</t>
+  </si>
+  <si>
+    <t>=ХИ2.РАСП(2;3;ЛОЖЬ)</t>
+  </si>
+  <si>
+    <t>CHISQ.DIST.RT(18.307,10)</t>
+  </si>
+  <si>
+    <t>=ХИ2.РАСП.ПХ(18,307;10)</t>
+  </si>
+  <si>
+    <t>CHIDIST(18.307,10)</t>
+  </si>
+  <si>
+    <t>=ХИ2РАСП(18,307;10)</t>
+  </si>
+  <si>
+    <t>CHISQ.INV(0.93,1)</t>
+  </si>
+  <si>
+    <t>=ХИ2.ОБР(0,93;1)</t>
+  </si>
+  <si>
+    <t>CHISQ.INV(0.6,2)</t>
+  </si>
+  <si>
+    <t>=ХИ2.ОБР(0,6;2)</t>
+  </si>
+  <si>
+    <t>CHISQ.INV.RT(0.050001,10)</t>
+  </si>
+  <si>
+    <t>=ХИ2.ОБР.ПХ(0,050001;10)</t>
+  </si>
+  <si>
+    <t>CHIINV(0.05,10)</t>
+  </si>
+  <si>
+    <t>=ХИ2ОБР(0,05;10)</t>
+  </si>
+  <si>
+    <t>CHISQ.TEST({58,35;11,25;10,23},{45.35,47.65;17.56,18.44;16.09,16.91})</t>
+  </si>
+  <si>
+    <t>=ХИ2.ТЕСТ({58;35:11;25:10;23};{45,35;47,65:17,56;18,44:16,09;16,91})</t>
+  </si>
+  <si>
+    <t>CHITEST({10,20,30},{15,20,25})</t>
+  </si>
+  <si>
+    <t>=ХИ2ТЕСТ({10;20;30};{15;20;25})</t>
+  </si>
+  <si>
+    <t>EXPON.DIST(0.2,10,TRUE)</t>
+  </si>
+  <si>
+    <t>=ЭКСП.РАСП(0,2;10;ИСТИНА)</t>
+  </si>
+  <si>
+    <t>EXPON.DIST(0.2,10,FALSE)</t>
+  </si>
+  <si>
+    <t>=ЭКСП.РАСП(0,2;10;ЛОЖЬ)</t>
+  </si>
+  <si>
+    <t>EXPONDIST(1,2,TRUE)</t>
+  </si>
+  <si>
+    <t>=ЭКСПРАСП(1;2;ИСТИНА)</t>
+  </si>
+  <si>
+    <t>F.DIST(15.2069,6,4,TRUE)</t>
+  </si>
+  <si>
+    <t>=F.РАСП(15,2069;6;4;ИСТИНА)</t>
+  </si>
+  <si>
+    <t>F.DIST(15.2069,6,4,FALSE)</t>
+  </si>
+  <si>
+    <t>=F.РАСП(15,2069;6;4;ЛОЖЬ)</t>
+  </si>
+  <si>
+    <t>F.DIST.RT(15.2069,6,4)</t>
+  </si>
+  <si>
+    <t>=F.РАСП.ПХ(15,2069;6;4)</t>
+  </si>
+  <si>
+    <t>FDIST(2,5,10)</t>
+  </si>
+  <si>
+    <t>=FРАСП(2;5;10)</t>
+  </si>
+  <si>
+    <t>F.INV(0.01,6,4)</t>
+  </si>
+  <si>
+    <t>=F.ОБР(0,01;6;4)</t>
+  </si>
+  <si>
+    <t>F.INV.RT(0.01,6,4)</t>
+  </si>
+  <si>
+    <t>=F.ОБР.ПХ(0,01;6;4)</t>
+  </si>
+  <si>
+    <t>FINV(0.05,3,20)</t>
+  </si>
+  <si>
+    <t>=FРАСПОБР(0,05;3;20)</t>
+  </si>
+  <si>
+    <t>F.TEST(Данные!C2:C11,Данные!E2:E11)</t>
+  </si>
+  <si>
+    <t>=F.ТЕСТ(Данные!C2:C11;Данные!E2:E11)</t>
+  </si>
+  <si>
+    <t>FTEST({6,7,9,15,21},{20,28,31,38,40})</t>
+  </si>
+  <si>
+    <t>=ФТЕСТ({6;7;9;15;21};{20;28;31;38;40})</t>
+  </si>
+  <si>
+    <t>GAMMA(2.5)</t>
+  </si>
+  <si>
+    <t>=ГАММА(2,5)</t>
+  </si>
+  <si>
+    <t>GAMMA(-0.75)</t>
+  </si>
+  <si>
+    <t>=ГАММА(-0,75)</t>
+  </si>
+  <si>
+    <t>GAMMA(0)</t>
+  </si>
+  <si>
+    <t>=ГАММА(0)</t>
+  </si>
+  <si>
+    <t>GAMMA(10)</t>
+  </si>
+  <si>
+    <t>=ГАММА(10)</t>
+  </si>
+  <si>
+    <t>GAMMA.DIST(10.00001131,9,2,FALSE)</t>
+  </si>
+  <si>
+    <t>=ГАММА.РАСП(10,00001131;9;2;ЛОЖЬ)</t>
+  </si>
+  <si>
+    <t>GAMMA.DIST(10.00001131,9,2,TRUE)</t>
+  </si>
+  <si>
+    <t>=ГАММА.РАСП(10,00001131;9;2;ИСТИНА)</t>
+  </si>
+  <si>
+    <t>GAMMADIST(3,2,1,TRUE)</t>
+  </si>
+  <si>
+    <t>=ГАММАРАСП(3;2;1;ИСТИНА)</t>
+  </si>
+  <si>
+    <t>GAMMA.INV(0.068094,9,2)</t>
+  </si>
+  <si>
+    <t>=ГАММА.ОБР(0,068094;9;2)</t>
+  </si>
+  <si>
+    <t>GAMMAINV(0.5,3,2)</t>
+  </si>
+  <si>
+    <t>=ГАММАОБР(0,5;3;2)</t>
+  </si>
+  <si>
+    <t>GAMMALN(4)</t>
+  </si>
+  <si>
+    <t>=ГАММАНЛОГ(4)</t>
+  </si>
+  <si>
+    <t>GAMMALN(0.5)</t>
+  </si>
+  <si>
+    <t>=ГАММАНЛОГ(0,5)</t>
+  </si>
+  <si>
+    <t>GAMMALN.PRECISE(100)</t>
+  </si>
+  <si>
+    <t>=ГАММАНЛОГ.ТОЧН(100)</t>
+  </si>
+  <si>
+    <t>HYPGEOM.DIST(1,4,8,20,TRUE)</t>
+  </si>
+  <si>
+    <t>=ГИПЕРГЕОМ.РАСП(1;4;8;20;ИСТИНА)</t>
+  </si>
+  <si>
+    <t>HYPGEOM.DIST(1,4,8,20,FALSE)</t>
+  </si>
+  <si>
+    <t>=ГИПЕРГЕОМ.РАСП(1;4;8;20;ЛОЖЬ)</t>
+  </si>
+  <si>
+    <t>HYPGEOMDIST(2,10,5,30)</t>
+  </si>
+  <si>
+    <t>=ГИПЕРГЕОМЕТ(2;10;5;30)</t>
+  </si>
+  <si>
+    <t>LOGNORM.DIST(4,3.5,1.2,TRUE)</t>
+  </si>
+  <si>
+    <t>=ЛОГНОРМ.РАСП(4;3,5;1,2;ИСТИНА)</t>
+  </si>
+  <si>
+    <t>LOGNORM.DIST(4,3.5,1.2,FALSE)</t>
+  </si>
+  <si>
+    <t>=ЛОГНОРМ.РАСП(4;3,5;1,2;ЛОЖЬ)</t>
+  </si>
+  <si>
+    <t>LOGNORMDIST(4,3.5,1.2)</t>
+  </si>
+  <si>
+    <t>=ЛОГНОРМРАСП(4;3,5;1,2)</t>
+  </si>
+  <si>
+    <t>LOGNORM.INV(0.039084,3.5,1.2)</t>
+  </si>
+  <si>
+    <t>=ЛОГНОРМ.ОБР(0,039084;3,5;1,2)</t>
+  </si>
+  <si>
+    <t>LOGINV(0.5,0,1)</t>
+  </si>
+  <si>
+    <t>=ЛОГНОРМОБР(0,5;0;1)</t>
+  </si>
+  <si>
+    <t>NEGBINOM.DIST(10,5,0.25,TRUE)</t>
+  </si>
+  <si>
+    <t>=ОТРБИНОМ.РАСП(10;5;0,25;ИСТИНА)</t>
+  </si>
+  <si>
+    <t>NEGBINOM.DIST(10,5,0.25,FALSE)</t>
+  </si>
+  <si>
+    <t>=ОТРБИНОМ.РАСП(10;5;0,25;ЛОЖЬ)</t>
+  </si>
+  <si>
+    <t>NEGBINOMDIST(3,2,0.5)</t>
+  </si>
+  <si>
+    <t>=ОТРБИНОМРАСП(3;2;0,5)</t>
+  </si>
+  <si>
+    <t>POISSON.DIST(2,5,TRUE)</t>
+  </si>
+  <si>
+    <t>=ПУАССОН.РАСП(2;5;ИСТИНА)</t>
+  </si>
+  <si>
+    <t>POISSON.DIST(2,5,FALSE)</t>
+  </si>
+  <si>
+    <t>=ПУАССОН.РАСП(2;5;ЛОЖЬ)</t>
+  </si>
+  <si>
+    <t>POISSON(10,7,TRUE)</t>
+  </si>
+  <si>
+    <t>=ПУАССОН(10;7;ИСТИНА)</t>
+  </si>
+  <si>
+    <t>T.DIST(60,1,TRUE)</t>
+  </si>
+  <si>
+    <t>=СТЬЮДЕНТ.РАСП(60;1;ИСТИНА)</t>
+  </si>
+  <si>
+    <t>T.DIST(8,3,FALSE)</t>
+  </si>
+  <si>
+    <t>=СТЬЮДЕНТ.РАСП(8;3;ЛОЖЬ)</t>
+  </si>
+  <si>
+    <t>T.DIST(-1.5,4,TRUE)</t>
+  </si>
+  <si>
+    <t>=СТЬЮДЕНТ.РАСП(-1,5;4;ИСТИНА)</t>
+  </si>
+  <si>
+    <t>T.DIST.2T(1.959999998,60)</t>
+  </si>
+  <si>
+    <t>=СТЬЮДЕНТ.РАСП.2Х(1,959999998;60)</t>
+  </si>
+  <si>
+    <t>T.DIST.RT(1.959999998,60)</t>
+  </si>
+  <si>
+    <t>=СТЬЮДЕНТ.РАСП.ПХ(1,959999998;60)</t>
+  </si>
+  <si>
+    <t>TDIST(1.96,60,2)</t>
+  </si>
+  <si>
+    <t>=СТЬЮДРАСП(1,96;60;2)</t>
+  </si>
+  <si>
+    <t>TDIST(1.96,60,1)</t>
+  </si>
+  <si>
+    <t>=СТЬЮДРАСП(1,96;60;1)</t>
+  </si>
+  <si>
+    <t>T.INV(0.75,2)</t>
+  </si>
+  <si>
+    <t>=СТЬЮДЕНТ.ОБР(0,75;2)</t>
+  </si>
+  <si>
+    <t>T.INV(0.05,10)</t>
+  </si>
+  <si>
+    <t>=СТЬЮДЕНТ.ОБР(0,05;10)</t>
+  </si>
+  <si>
+    <t>T.INV.2T(0.546449,60)</t>
+  </si>
+  <si>
+    <t>=СТЬЮДЕНТ.ОБР.2Х(0,546449;60)</t>
+  </si>
+  <si>
+    <t>TINV(0.05,30)</t>
+  </si>
+  <si>
+    <t>=СТЬЮДРАСПОБР(0,05;30)</t>
+  </si>
+  <si>
+    <t>T.TEST({3,4,5,8,9,1,2,4,5},{6,19,3,2,14,4,5,17,1},2,1)</t>
+  </si>
+  <si>
+    <t>=СТЬЮДЕНТ.ТЕСТ({3;4;5;8;9;1;2;4;5};{6;19;3;2;14;4;5;17;1};2;1)</t>
+  </si>
+  <si>
+    <t>T.TEST(Данные!C2:C6,Данные!C7:C11,2,2)</t>
+  </si>
+  <si>
+    <t>=СТЬЮДЕНТ.ТЕСТ(Данные!C2:C6;Данные!C7:C11;2;2)</t>
+  </si>
+  <si>
+    <t>T.TEST(Данные!C2:C6,Данные!C7:C11,1,3)</t>
+  </si>
+  <si>
+    <t>=СТЬЮДЕНТ.ТЕСТ(Данные!C2:C6;Данные!C7:C11;1;3)</t>
+  </si>
+  <si>
+    <t>TTEST({1,2,3,4},{2,4,6,9},2,3)</t>
+  </si>
+  <si>
+    <t>=ТТЕСТ({1;2;3;4};{2;4;6;9};2;3)</t>
+  </si>
+  <si>
+    <t>WEIBULL.DIST(105,20,100,TRUE)</t>
+  </si>
+  <si>
+    <t>=ВЕЙБУЛЛ.РАСП(105;20;100;ИСТИНА)</t>
+  </si>
+  <si>
+    <t>WEIBULL.DIST(105,20,100,FALSE)</t>
+  </si>
+  <si>
+    <t>=ВЕЙБУЛЛ.РАСП(105;20;100;ЛОЖЬ)</t>
+  </si>
+  <si>
+    <t>WEIBULL(2,1.5,3,TRUE)</t>
+  </si>
+  <si>
+    <t>=ВЕЙБУЛЛ(2;1,5;3;ИСТИНА)</t>
+  </si>
+  <si>
+    <t>Z.TEST({3,6,7,8,6,5,4,2,1,9},4)</t>
+  </si>
+  <si>
+    <t>=Z.ТЕСТ({3;6;7;8;6;5;4;2;1;9};4)</t>
+  </si>
+  <si>
+    <t>Z.TEST({3,6,7,8,6,5,4,2,1,9},6,2)</t>
+  </si>
+  <si>
+    <t>=Z.ТЕСТ({3;6;7;8;6;5;4;2;1;9};6;2)</t>
+  </si>
+  <si>
+    <t>ZTEST(Данные!E2:E11,3)</t>
+  </si>
+  <si>
+    <t>=ZТЕСТ(Данные!E2:E11;3)</t>
+  </si>
+  <si>
+    <t>CONFIDENCE.T(0.05,1,50)</t>
+  </si>
+  <si>
+    <t>=ДОВЕРИТ.СТЬЮДЕНТ(0,05;1;50)</t>
+  </si>
+  <si>
+    <t>CONFIDENCE.T(0.1,2.5,12)</t>
+  </si>
+  <si>
+    <t>=ДОВЕРИТ.СТЬЮДЕНТ(0,1;2,5;12)</t>
   </si>
 </sst>
 </file>
@@ -4326,7 +4833,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19719C88-43A0-490E-9ACF-B4029777B49B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9708CB57-437B-4466-8C2F-E64665FAB591}">
   <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4645,7 +5152,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AC5F0B4-F12D-47CA-9FB5-9195E4939F15}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0900CAF3-6137-44AA-8756-37F156F3FFA2}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4665,7 +5172,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DE222B-A967-4A91-A756-86129C4D11E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5CCF40D-D609-466D-BB8D-55E4107479EC}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4685,7 +5192,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{397D33EA-D7C5-41F0-B6F0-0402027F1282}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23589D58-52CF-453B-85BD-D1E0CB5BBE30}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4705,8 +5212,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1382C3C4-B80B-4B76-8725-6BB3A856B5BF}">
-  <dimension ref="A1:E624"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FB24E1F-3126-426E-91C5-2FB016B686C1}">
+  <dimension ref="A1:E708"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.140625" style="1"/>
@@ -10068,7 +10575,7 @@
       </c>
       <c r="C358" s="7">
         <f ca="1">NOW()</f>
-        <v>46305.827894444446</v>
+        <v>46305.830834837965</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>757</v>
@@ -10083,7 +10590,7 @@
       </c>
       <c r="C359">
         <f ca="1">RAND()</f>
-        <v>0.47319959542677592</v>
+        <v>0.30101712173518425</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>759</v>
@@ -14062,6 +14569,1266 @@
       </c>
       <c r="E624" s="1" t="s">
         <v>1291</v>
+      </c>
+    </row>
+    <row r="625" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A625" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B625" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C625">
+        <f>_xlfn.BETA.DIST(0.4,2,3,TRUE)</f>
+        <v>0.52480000000000004</v>
+      </c>
+      <c r="E625" s="1" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="626" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A626" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B626" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C626">
+        <f>_xlfn.BETA.DIST(0.4,2,3,FALSE)</f>
+        <v>1.728</v>
+      </c>
+      <c r="E626" s="1" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="627" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A627" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B627" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C627">
+        <f>_xlfn.BETA.DIST(2,8,10,TRUE,1,3)</f>
+        <v>0.68547058105468728</v>
+      </c>
+      <c r="E627" s="1" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="628" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A628" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B628" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C628">
+        <f>BETADIST(2,8,10,1,3)</f>
+        <v>0.68547058105468728</v>
+      </c>
+      <c r="E628" s="1" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="629" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A629" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B629" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C629">
+        <f>_xlfn.BETA.INV(0.685470581,8,10,1,3)</f>
+        <v>1.9999999999631426</v>
+      </c>
+      <c r="E629" s="1" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="630" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A630" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B630" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C630">
+        <f>BETAINV(0.2,4,5)</f>
+        <v>0.30322584466408187</v>
+      </c>
+      <c r="E630" s="1" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="631" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A631" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B631" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C631">
+        <f>_xlfn.BINOM.DIST(6,10,0.5,FALSE)</f>
+        <v>0.20507812500000006</v>
+      </c>
+      <c r="E631" s="1" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="632" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A632" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B632" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C632">
+        <f>_xlfn.BINOM.DIST(6,10,0.5,TRUE)</f>
+        <v>0.828125</v>
+      </c>
+      <c r="E632" s="1" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="633" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A633" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B633" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C633">
+        <f>BINOMDIST(3,8,0.25,TRUE)</f>
+        <v>0.8861846923828125</v>
+      </c>
+      <c r="E633" s="1" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="634" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A634" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C634">
+        <f>_xlfn.BINOM.DIST.RANGE(60,0.75,48)</f>
+        <v>8.3974967429047503E-2</v>
+      </c>
+      <c r="E634" s="1" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="635" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A635" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B635" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C635">
+        <f>_xlfn.BINOM.DIST.RANGE(60,0.75,45,50)</f>
+        <v>0.52362979347188721</v>
+      </c>
+      <c r="E635" s="1" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="636" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A636" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B636" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C636">
+        <f>_xlfn.BINOM.INV(6,0.5,0.75)</f>
+        <v>4</v>
+      </c>
+      <c r="E636" s="1" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="637" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A637" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B637" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C637">
+        <f>CRITBINOM(10,0.3,0.5)</f>
+        <v>3</v>
+      </c>
+      <c r="E637" s="1" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="638" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A638" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B638" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C638">
+        <f>_xlfn.CHISQ.DIST(0.5,1,TRUE)</f>
+        <v>0.52049987781304652</v>
+      </c>
+      <c r="E638" s="1" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="639" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A639" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B639" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C639">
+        <f>_xlfn.CHISQ.DIST(2,3,FALSE)</f>
+        <v>0.20755374871029736</v>
+      </c>
+      <c r="E639" s="1" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="640" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A640" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B640" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C640">
+        <f>_xlfn.CHISQ.DIST.RT(18.307,10)</f>
+        <v>5.0000589091398109E-2</v>
+      </c>
+      <c r="E640" s="1" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="641" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A641" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B641" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C641">
+        <f>CHIDIST(18.307,10)</f>
+        <v>5.0000589091398109E-2</v>
+      </c>
+      <c r="E641" s="1" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="642" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A642" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B642" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C642">
+        <f>_xlfn.CHISQ.INV(0.93,1)</f>
+        <v>3.2830202867595295</v>
+      </c>
+      <c r="E642" s="1" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="643" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A643" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B643" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C643">
+        <f>_xlfn.CHISQ.INV(0.6,2)</f>
+        <v>1.83258146374831</v>
+      </c>
+      <c r="E643" s="1" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="644" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A644" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B644" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C644">
+        <f>_xlfn.CHISQ.INV.RT(0.050001,10)</f>
+        <v>18.306973456961057</v>
+      </c>
+      <c r="E644" s="1" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="645" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A645" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B645" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C645">
+        <f>CHIINV(0.05,10)</f>
+        <v>18.307038053275146</v>
+      </c>
+      <c r="E645" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="646" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A646" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B646" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C646">
+        <f>_xlfn.CHISQ.TEST({58,35;11,25;10,23},{45.35,47.65;17.56,18.44;16.09,16.91})</f>
+        <v>3.0819201700830936E-4</v>
+      </c>
+      <c r="E646" s="1" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="647" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A647" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B647" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C647">
+        <f>CHITEST({10,20,30},{15,20,25})</f>
+        <v>0.26359713811572671</v>
+      </c>
+      <c r="E647" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="648" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A648" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B648" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C648">
+        <f>_xlfn.EXPON.DIST(0.2,10,TRUE)</f>
+        <v>0.8646647167633873</v>
+      </c>
+      <c r="E648" s="1" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="649" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A649" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B649" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C649">
+        <f>_xlfn.EXPON.DIST(0.2,10,FALSE)</f>
+        <v>1.353352832366127</v>
+      </c>
+      <c r="E649" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="650" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A650" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B650" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C650">
+        <f>EXPONDIST(1,2,TRUE)</f>
+        <v>0.8646647167633873</v>
+      </c>
+      <c r="E650" s="1" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="651" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A651" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B651" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C651">
+        <f>_xlfn.F.DIST(15.2069,6,4,TRUE)</f>
+        <v>0.99000004300276268</v>
+      </c>
+      <c r="E651" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="652" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A652" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B652" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C652">
+        <f>_xlfn.F.DIST(15.2069,6,4,FALSE)</f>
+        <v>1.2237917087831725E-3</v>
+      </c>
+      <c r="E652" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="653" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A653" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B653" s="1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C653">
+        <f>_xlfn.F.DIST.RT(15.2069,6,4)</f>
+        <v>9.9999569972373126E-3</v>
+      </c>
+      <c r="E653" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="654" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A654" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B654" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C654">
+        <f>FDIST(2,5,10)</f>
+        <v>0.16419495089973879</v>
+      </c>
+      <c r="E654" s="1" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="655" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A655" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B655" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C655">
+        <f>_xlfn.F.INV(0.01,6,4)</f>
+        <v>0.10930991412457855</v>
+      </c>
+      <c r="E655" s="1" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="656" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A656" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B656" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C656">
+        <f>_xlfn.F.INV.RT(0.01,6,4)</f>
+        <v>15.206864861157531</v>
+      </c>
+      <c r="E656" s="1" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="657" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A657" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B657" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C657">
+        <f>FINV(0.05,3,20)</f>
+        <v>3.0983912121407795</v>
+      </c>
+      <c r="E657" s="1" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="658" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A658" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B658" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C658">
+        <f>_xlfn.F.TEST(Данные!C2:C11,Данные!E2:E11)</f>
+        <v>1.9895153405513282E-23</v>
+      </c>
+      <c r="E658" s="1" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="659" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A659" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B659" s="1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C659">
+        <f>FTEST({6,7,9,15,21},{20,28,31,38,40})</f>
+        <v>0.64831784678617432</v>
+      </c>
+      <c r="E659" s="1" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="660" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A660" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B660" s="1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C660">
+        <f>_xlfn.GAMMA(2.5)</f>
+        <v>1.329340388179137</v>
+      </c>
+      <c r="E660" s="1" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="661" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A661" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B661" s="1" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C661">
+        <f>_xlfn.GAMMA(-0.75)</f>
+        <v>-4.8341465442958782</v>
+      </c>
+      <c r="E661" s="1" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="662" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A662" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B662" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C662" t="e">
+        <f>_xlfn.GAMMA(0)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="E662" s="1" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="663" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A663" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B663" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C663">
+        <f>_xlfn.GAMMA(10)</f>
+        <v>362880</v>
+      </c>
+      <c r="E663" s="1" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="664" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A664" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B664" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C664">
+        <f>_xlfn.GAMMA.DIST(10.00001131,9,2,FALSE)</f>
+        <v>3.2639130418294013E-2</v>
+      </c>
+      <c r="E664" s="1" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="665" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A665" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B665" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C665">
+        <f>_xlfn.GAMMA.DIST(10.00001131,9,2,TRUE)</f>
+        <v>6.809400386978734E-2</v>
+      </c>
+      <c r="E665" s="1" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="666" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A666" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C666">
+        <f>GAMMADIST(3,2,1,TRUE)</f>
+        <v>0.80085172652854419</v>
+      </c>
+      <c r="E666" s="1" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="667" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A667" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B667" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C667">
+        <f>_xlfn.GAMMA.INV(0.068094,9,2)</f>
+        <v>10.00001119143718</v>
+      </c>
+      <c r="E667" s="1" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="668" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A668" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B668" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C668">
+        <f>GAMMAINV(0.5,3,2)</f>
+        <v>5.3481206274471216</v>
+      </c>
+      <c r="E668" s="1" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="669" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A669" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B669" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C669">
+        <f>GAMMALN(4)</f>
+        <v>1.791759469228055</v>
+      </c>
+      <c r="E669" s="1" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="670" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A670" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B670" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C670">
+        <f>GAMMALN(0.5)</f>
+        <v>0.57236494292470008</v>
+      </c>
+      <c r="E670" s="1" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="671" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A671" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C671">
+        <f>_xlfn.GAMMALN.PRECISE(100)</f>
+        <v>359.1342053695754</v>
+      </c>
+      <c r="E671" s="1" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="672" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A672" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B672" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C672">
+        <f>_xlfn.HYPGEOM.DIST(1,4,8,20,TRUE)</f>
+        <v>0.46542827657378727</v>
+      </c>
+      <c r="E672" s="1" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="673" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A673" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B673" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C673">
+        <f>_xlfn.HYPGEOM.DIST(1,4,8,20,FALSE)</f>
+        <v>0.36326109391124861</v>
+      </c>
+      <c r="E673" s="1" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="674" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A674" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B674" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C674">
+        <f>HYPGEOMDIST(2,10,5,30)</f>
+        <v>0.35998484274346321</v>
+      </c>
+      <c r="E674" s="1" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="675" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A675" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B675" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C675">
+        <f>_xlfn.LOGNORM.DIST(4,3.5,1.2,TRUE)</f>
+        <v>3.9083555706800478E-2</v>
+      </c>
+      <c r="E675" s="1" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="676" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A676" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B676" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C676">
+        <f>_xlfn.LOGNORM.DIST(4,3.5,1.2,FALSE)</f>
+        <v>1.7617596681819218E-2</v>
+      </c>
+      <c r="E676" s="1" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="677" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A677" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B677" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C677">
+        <f>LOGNORMDIST(4,3.5,1.2)</f>
+        <v>3.9083555706800478E-2</v>
+      </c>
+      <c r="E677" s="1" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="678" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A678" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C678">
+        <f>_xlfn.LOGNORM.INV(0.039084,3.5,1.2)</f>
+        <v>4.000025218680638</v>
+      </c>
+      <c r="E678" s="1" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="679" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A679" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B679" s="1" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C679">
+        <f>LOGINV(0.5,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="E679" s="1" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="680" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A680" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B680" s="1" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C680">
+        <f>_xlfn.NEGBINOM.DIST(10,5,0.25,TRUE)</f>
+        <v>0.31351405847817665</v>
+      </c>
+      <c r="E680" s="1" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="681" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A681" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C681">
+        <f>_xlfn.NEGBINOM.DIST(10,5,0.25,FALSE)</f>
+        <v>5.5048660375177853E-2</v>
+      </c>
+      <c r="E681" s="1" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="682" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A682" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B682" s="1" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C682">
+        <f>NEGBINOMDIST(3,2,0.5)</f>
+        <v>0.12499999999999996</v>
+      </c>
+      <c r="E682" s="1" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="683" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A683" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B683" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C683">
+        <f>_xlfn.POISSON.DIST(2,5,TRUE)</f>
+        <v>0.12465201948308113</v>
+      </c>
+      <c r="E683" s="1" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="684" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A684" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B684" s="1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C684">
+        <f>_xlfn.POISSON.DIST(2,5,FALSE)</f>
+        <v>8.4224337488568335E-2</v>
+      </c>
+      <c r="E684" s="1" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="685" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A685" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B685" s="1" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C685">
+        <f>POISSON(10,7,TRUE)</f>
+        <v>0.90147920588908714</v>
+      </c>
+      <c r="E685" s="1" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="686" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A686" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B686" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C686">
+        <f>_xlfn.T.DIST(60,1,TRUE)</f>
+        <v>0.99469532636737668</v>
+      </c>
+      <c r="E686" s="1" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="687" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A687" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B687" s="1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C687">
+        <f>_xlfn.T.DIST(8,3,FALSE)</f>
+        <v>7.3690652094692661E-4</v>
+      </c>
+      <c r="E687" s="1" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="688" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A688" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B688" s="1" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C688">
+        <f>_xlfn.T.DIST(-1.5,4,TRUE)</f>
+        <v>0.10399999999999993</v>
+      </c>
+      <c r="E688" s="1" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="689" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A689" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B689" s="1" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C689">
+        <f>_xlfn.T.DIST.2T(1.959999998,60)</f>
+        <v>5.4644929975920957E-2</v>
+      </c>
+      <c r="E689" s="1" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="690" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A690" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B690" s="1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C690">
+        <f>_xlfn.T.DIST.RT(1.959999998,60)</f>
+        <v>2.7322464987960478E-2</v>
+      </c>
+      <c r="E690" s="1" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="691" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A691" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B691" s="1" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C691">
+        <f>TDIST(1.96,60,2)</f>
+        <v>5.4644929736529339E-2</v>
+      </c>
+      <c r="E691" s="1" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="692" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A692" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B692" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C692">
+        <f>TDIST(1.96,60,1)</f>
+        <v>2.732246486826467E-2</v>
+      </c>
+      <c r="E692" s="1" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="693" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A693" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C693">
+        <f>_xlfn.T.INV(0.75,2)</f>
+        <v>0.81649658092772592</v>
+      </c>
+      <c r="E693" s="1" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="694" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A694" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B694" s="1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C694">
+        <f>_xlfn.T.INV(0.05,10)</f>
+        <v>-1.812461122811676</v>
+      </c>
+      <c r="E694" s="1" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="695" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A695" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B695" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C695">
+        <f>_xlfn.T.INV.2T(0.546449,60)</f>
+        <v>0.60653307582575899</v>
+      </c>
+      <c r="E695" s="1" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="696" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A696" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B696" s="1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C696">
+        <f>TINV(0.05,30)</f>
+        <v>2.0422724563012378</v>
+      </c>
+      <c r="E696" s="1" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="697" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A697" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B697" s="1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C697">
+        <f>_xlfn.T.TEST({3,4,5,8,9,1,2,4,5},{6,19,3,2,14,4,5,17,1},2,1)</f>
+        <v>0.19601578492528193</v>
+      </c>
+      <c r="E697" s="1" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="698" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A698" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B698" s="1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C698">
+        <f>_xlfn.T.TEST(Данные!C2:C6,Данные!C7:C11,2,2)</f>
+        <v>0.68139091316772538</v>
+      </c>
+      <c r="E698" s="1" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="699" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A699" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C699">
+        <f>_xlfn.T.TEST(Данные!C2:C6,Данные!C7:C11,1,3)</f>
+        <v>0.34101896362342221</v>
+      </c>
+      <c r="E699" s="1" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="700" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A700" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B700" s="1" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C700">
+        <f>TTEST({1,2,3,4},{2,4,6,9},2,3)</f>
+        <v>0.16470207962805669</v>
+      </c>
+      <c r="E700" s="1" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="701" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A701" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B701" s="1" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C701">
+        <f>_xlfn.WEIBULL.DIST(105,20,100,TRUE)</f>
+        <v>0.92958139006927698</v>
+      </c>
+      <c r="E701" s="1" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="702" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A702" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B702" s="1" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C702">
+        <f>_xlfn.WEIBULL.DIST(105,20,100,FALSE)</f>
+        <v>3.5588864024503564E-2</v>
+      </c>
+      <c r="E702" s="1" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="703" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A703" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B703" s="1" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C703">
+        <f>WEIBULL(2,1.5,3,TRUE)</f>
+        <v>0.41977020402532705</v>
+      </c>
+      <c r="E703" s="1" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="704" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A704" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B704" s="1" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C704">
+        <f>_xlfn.Z.TEST({3,6,7,8,6,5,4,2,1,9},4)</f>
+        <v>9.0574196851363808E-2</v>
+      </c>
+      <c r="E704" s="1" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="705" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A705" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B705" s="1" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C705">
+        <f>_xlfn.Z.TEST({3,6,7,8,6,5,4,2,1,9},6,2)</f>
+        <v>0.92263553825731093</v>
+      </c>
+      <c r="E705" s="1" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="706" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A706" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B706" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C706">
+        <f>ZTEST(Данные!E2:E11,3)</f>
+        <v>0.12883847438935495</v>
+      </c>
+      <c r="E706" s="1" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="707" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A707" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B707" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C707">
+        <f>_xlfn.CONFIDENCE.T(0.05,1,50)</f>
+        <v>0.28419685549572982</v>
+      </c>
+      <c r="E707" s="1" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="708" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A708" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B708" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C708">
+        <f>_xlfn.CONFIDENCE.T(0.1,2.5,12)</f>
+        <v>1.2960682293904275</v>
+      </c>
+      <c r="E708" s="1" t="s">
+        <v>1460</v>
       </c>
     </row>
   </sheetData>

--- a/tests/fixtures/formulas.xlsx
+++ b/tests/fixtures/formulas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\New_Office\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBDC992A-0119-4403-AEE2-D29DE71248DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{067A265D-5E88-4507-AD56-FAFAAB4C6990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{2A13D604-5984-403D-890D-D13B94968E51}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{DD5682B5-DED2-461D-A0CC-D388BB63C15D}"/>
   </bookViews>
   <sheets>
     <sheet name="Данные" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2171" uniqueCount="1461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2435" uniqueCount="1638">
   <si>
     <t>Имя</t>
   </si>
@@ -4447,6 +4447,537 @@
   </si>
   <si>
     <t>=ДОВЕРИТ.СТЬЮДЕНТ(0,1;2,5;12)</t>
+  </si>
+  <si>
+    <t>Пакет C: комплексные числа, Бессель, ПРЕОБР</t>
+  </si>
+  <si>
+    <t>COMPLEX(3,4)</t>
+  </si>
+  <si>
+    <t>=КОМПЛЕКСН(3;4)</t>
+  </si>
+  <si>
+    <t>COMPLEX(3,4,"j")</t>
+  </si>
+  <si>
+    <t>=КОМПЛЕКСН(3;4;"j")</t>
+  </si>
+  <si>
+    <t>COMPLEX(0,1)</t>
+  </si>
+  <si>
+    <t>=КОМПЛЕКСН(0;1)</t>
+  </si>
+  <si>
+    <t>COMPLEX(0,-1)</t>
+  </si>
+  <si>
+    <t>=КОМПЛЕКСН(0;-1)</t>
+  </si>
+  <si>
+    <t>COMPLEX(1.5,0)</t>
+  </si>
+  <si>
+    <t>=КОМПЛЕКСН(1,5;0)</t>
+  </si>
+  <si>
+    <t>COMPLEX(-2.5,-0.5)</t>
+  </si>
+  <si>
+    <t>=КОМПЛЕКСН(-2,5;-0,5)</t>
+  </si>
+  <si>
+    <t>IMABS("5+12i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.ABS("5+12i")</t>
+  </si>
+  <si>
+    <t>IMAGINARY("3+4i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.ЧАСТЬ("3+4i")</t>
+  </si>
+  <si>
+    <t>IMAGINARY("-i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.ЧАСТЬ("-i")</t>
+  </si>
+  <si>
+    <t>IMREAL("6-9i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.ВЕЩ("6-9i")</t>
+  </si>
+  <si>
+    <t>IMARGUMENT("3+4i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.АРГУМЕНТ("3+4i")</t>
+  </si>
+  <si>
+    <t>IMCONJUGATE("3+4i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.СОПРЯЖ("3+4i")</t>
+  </si>
+  <si>
+    <t>IMCOS("1+i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.COS("1+i")</t>
+  </si>
+  <si>
+    <t>IMCOSH("4+3i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.COSH("4+3i")</t>
+  </si>
+  <si>
+    <t>IMCOT("4+3i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.COT("4+3i")</t>
+  </si>
+  <si>
+    <t>IMCSC("4+3i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.CSC("4+3i")</t>
+  </si>
+  <si>
+    <t>IMCSCH("4+3i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.CSCH("4+3i")</t>
+  </si>
+  <si>
+    <t>IMDIV("-238+240i","10+24i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.ДЕЛ("-238+240i";"10+24i")</t>
+  </si>
+  <si>
+    <t>IMEXP("1+i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.EXP("1+i")</t>
+  </si>
+  <si>
+    <t>IMLN("3+4i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.LN("3+4i")</t>
+  </si>
+  <si>
+    <t>IMLOG10("3+4i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.LOG10("3+4i")</t>
+  </si>
+  <si>
+    <t>IMLOG2("3+4i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.LOG2("3+4i")</t>
+  </si>
+  <si>
+    <t>IMPOWER("2+3i",3)</t>
+  </si>
+  <si>
+    <t>=МНИМ.СТЕПЕНЬ("2+3i";3)</t>
+  </si>
+  <si>
+    <t>IMPOWER("2+3i",0.5)</t>
+  </si>
+  <si>
+    <t>=МНИМ.СТЕПЕНЬ("2+3i";0,5)</t>
+  </si>
+  <si>
+    <t>IMPRODUCT("3+4i","5-3i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.ПРОИЗВЕД("3+4i";"5-3i")</t>
+  </si>
+  <si>
+    <t>IMPRODUCT("1+2i",30)</t>
+  </si>
+  <si>
+    <t>=МНИМ.ПРОИЗВЕД("1+2i";30)</t>
+  </si>
+  <si>
+    <t>IMSEC("4+3i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.SEC("4+3i")</t>
+  </si>
+  <si>
+    <t>IMSECH("4+3i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.SECH("4+3i")</t>
+  </si>
+  <si>
+    <t>IMSIN("4+3i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.SIN("4+3i")</t>
+  </si>
+  <si>
+    <t>IMSINH("4+3i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.SINH("4+3i")</t>
+  </si>
+  <si>
+    <t>IMSQRT("1+i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.КОРЕНЬ("1+i")</t>
+  </si>
+  <si>
+    <t>IMSQRT("-4")</t>
+  </si>
+  <si>
+    <t>=МНИМ.КОРЕНЬ("-4")</t>
+  </si>
+  <si>
+    <t>IMSUB("13+4i","5+3i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.РАЗН("13+4i";"5+3i")</t>
+  </si>
+  <si>
+    <t>IMSUM("3+4i","5-3i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.СУММ("3+4i";"5-3i")</t>
+  </si>
+  <si>
+    <t>IMSUM("1+i","2-i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.СУММ("1+i";"2-i")</t>
+  </si>
+  <si>
+    <t>IMTAN("4+3i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.TAN("4+3i")</t>
+  </si>
+  <si>
+    <t>IMABS("1,5+2i")</t>
+  </si>
+  <si>
+    <t>=МНИМ.ABS("1,5+2i")</t>
+  </si>
+  <si>
+    <t>IMREAL("j")</t>
+  </si>
+  <si>
+    <t>=МНИМ.ВЕЩ("j")</t>
+  </si>
+  <si>
+    <t>BESSELI(1.5,1)</t>
+  </si>
+  <si>
+    <t>=БЕССЕЛЬ.I(1,5;1)</t>
+  </si>
+  <si>
+    <t>BESSELI(2.5,0)</t>
+  </si>
+  <si>
+    <t>=БЕССЕЛЬ.I(2,5;0)</t>
+  </si>
+  <si>
+    <t>BESSELI(4,3)</t>
+  </si>
+  <si>
+    <t>=БЕССЕЛЬ.I(4;3)</t>
+  </si>
+  <si>
+    <t>BESSELJ(1.9,2)</t>
+  </si>
+  <si>
+    <t>=БЕССЕЛЬ.J(1,9;2)</t>
+  </si>
+  <si>
+    <t>BESSELJ(10,0)</t>
+  </si>
+  <si>
+    <t>=БЕССЕЛЬ.J(10;0)</t>
+  </si>
+  <si>
+    <t>BESSELJ(0.5,1)</t>
+  </si>
+  <si>
+    <t>=БЕССЕЛЬ.J(0,5;1)</t>
+  </si>
+  <si>
+    <t>BESSELJ(15,5)</t>
+  </si>
+  <si>
+    <t>=БЕССЕЛЬ.J(15;5)</t>
+  </si>
+  <si>
+    <t>BESSELK(1.5,1)</t>
+  </si>
+  <si>
+    <t>=БЕССЕЛЬ.K(1,5;1)</t>
+  </si>
+  <si>
+    <t>BESSELK(0.5,0)</t>
+  </si>
+  <si>
+    <t>=БЕССЕЛЬ.K(0,5;0)</t>
+  </si>
+  <si>
+    <t>BESSELK(3,4)</t>
+  </si>
+  <si>
+    <t>=БЕССЕЛЬ.K(3;4)</t>
+  </si>
+  <si>
+    <t>BESSELY(2.5,1)</t>
+  </si>
+  <si>
+    <t>=БЕССЕЛЬ.Y(2,5;1)</t>
+  </si>
+  <si>
+    <t>BESSELY(10,0)</t>
+  </si>
+  <si>
+    <t>=БЕССЕЛЬ.Y(10;0)</t>
+  </si>
+  <si>
+    <t>BESSELY(1,3)</t>
+  </si>
+  <si>
+    <t>=БЕССЕЛЬ.Y(1;3)</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"lbm","kg")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"lbm";"kg")</t>
+  </si>
+  <si>
+    <t>CONVERT(68,"F","C")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(68;"F";"C")</t>
+  </si>
+  <si>
+    <t>CONVERT(2.5,"ft","sec")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(2,5;"ft";"sec")</t>
+  </si>
+  <si>
+    <t>CONVERT(CONVERT(100,"ft","m"),"ft","m")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(ПРЕОБР(100;"ft";"m");"ft";"m")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"mi","km")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"mi";"km")</t>
+  </si>
+  <si>
+    <t>CONVERT(10,"in","cm")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(10;"in";"cm")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"yr","day")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"yr";"day")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"atm","mmHg")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"atm";"mmHg")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"cal","J")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"cal";"J")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"HP","W")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"HP";"W")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"gal","l")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"gal";"l")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"uk_gal","l")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"uk_gal";"l")</t>
+  </si>
+  <si>
+    <t>CONVERT(100,"C","K")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(100;"C";"K")</t>
+  </si>
+  <si>
+    <t>CONVERT(0,"C","Rank")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(0;"C";"Rank")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"kn","m/s")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"kn";"m/s")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"mph","m/s")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"mph";"m/s")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"ha","m2")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"ha";"m2")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"km2","m2")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"km2";"m2")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"m3","l")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"m3";"l")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"Gibyte","bit")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"Gibyte";"bit")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"kbyte","byte")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"kbyte";"byte")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"BTU","J")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"BTU";"J")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"eV","J")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"eV";"J")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"T","ga")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"T";"ga")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"stone","kg")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"stone";"kg")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"ozm","g")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"ozm";"g")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"psi","Pa")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"psi";"Pa")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"Nmi","m")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"Nmi";"m")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"ly","m")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"ly";"m")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"cup","tsp")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"cup";"tsp")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"lbf","N")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"lbf";"N")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"Wh","J")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"Wh";"J")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"mm","ang")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"mm";"ang")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"ft3","l")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"ft3";"l")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"in2","cm2")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"in2";"cm2")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"barrel","gal")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"barrel";"gal")</t>
+  </si>
+  <si>
+    <t>CONVERT(1,"Reau","C")</t>
+  </si>
+  <si>
+    <t>=ПРЕОБР(1;"Reau";"C")</t>
   </si>
 </sst>
 </file>
@@ -4833,7 +5364,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9708CB57-437B-4466-8C2F-E64665FAB591}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0321EED-90EB-4541-8CEC-C44EE68CE245}">
   <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5152,7 +5683,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0900CAF3-6137-44AA-8756-37F156F3FFA2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC03273A-1695-4B7E-8AC4-41592AABC62C}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5172,7 +5703,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5CCF40D-D609-466D-BB8D-55E4107479EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537813D3-AD55-4462-B438-7027C06FC366}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5192,7 +5723,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23589D58-52CF-453B-85BD-D1E0CB5BBE30}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A70D965B-F6C3-408F-9473-14306BF4ECF4}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5212,8 +5743,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FB24E1F-3126-426E-91C5-2FB016B686C1}">
-  <dimension ref="A1:E708"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{435AC6E0-2581-4D1E-A765-BE261653750C}">
+  <dimension ref="A1:E796"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.140625" style="1"/>
@@ -10575,7 +11106,7 @@
       </c>
       <c r="C358" s="7">
         <f ca="1">NOW()</f>
-        <v>46305.830834837965</v>
+        <v>46305.833494560182</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>757</v>
@@ -10590,7 +11121,7 @@
       </c>
       <c r="C359">
         <f ca="1">RAND()</f>
-        <v>0.30101712173518425</v>
+        <v>0.70047170638689604</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>759</v>
@@ -10605,7 +11136,7 @@
       </c>
       <c r="C360">
         <f ca="1">RANDBETWEEN(1,10)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>761</v>
@@ -15829,6 +16360,1326 @@
       </c>
       <c r="E708" s="1" t="s">
         <v>1460</v>
+      </c>
+    </row>
+    <row r="709" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A709" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B709" s="1" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C709" t="str">
+        <f>COMPLEX(3,4)</f>
+        <v>3+4i</v>
+      </c>
+      <c r="E709" s="1" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="710" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A710" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B710" s="1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C710" t="str">
+        <f>COMPLEX(3,4,"j")</f>
+        <v>3+4j</v>
+      </c>
+      <c r="E710" s="1" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="711" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A711" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B711" s="1" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C711" t="str">
+        <f>COMPLEX(0,1)</f>
+        <v>i</v>
+      </c>
+      <c r="E711" s="1" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="712" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A712" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B712" s="1" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C712" t="str">
+        <f>COMPLEX(0,-1)</f>
+        <v>-i</v>
+      </c>
+      <c r="E712" s="1" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="713" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A713" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B713" s="1" t="s">
+        <v>1470</v>
+      </c>
+      <c r="C713" t="str">
+        <f>COMPLEX(1.5,0)</f>
+        <v>1,5</v>
+      </c>
+      <c r="E713" s="1" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="714" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A714" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B714" s="1" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C714" t="str">
+        <f>COMPLEX(-2.5,-0.5)</f>
+        <v>-2,5-0,5i</v>
+      </c>
+      <c r="E714" s="1" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="715" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A715" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B715" s="1" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C715">
+        <f>IMABS("5+12i")</f>
+        <v>13</v>
+      </c>
+      <c r="E715" s="1" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="716" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A716" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B716" s="1" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C716">
+        <f>IMAGINARY("3+4i")</f>
+        <v>4</v>
+      </c>
+      <c r="E716" s="1" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="717" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A717" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B717" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C717">
+        <f>IMAGINARY("-i")</f>
+        <v>-1</v>
+      </c>
+      <c r="E717" s="1" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="718" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A718" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B718" s="1" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C718">
+        <f>IMREAL("6-9i")</f>
+        <v>6</v>
+      </c>
+      <c r="E718" s="1" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="719" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A719" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B719" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="C719">
+        <f>IMARGUMENT("3+4i")</f>
+        <v>0.92729521800161219</v>
+      </c>
+      <c r="E719" s="1" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="720" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A720" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B720" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="C720" t="str">
+        <f>IMCONJUGATE("3+4i")</f>
+        <v>3-4i</v>
+      </c>
+      <c r="E720" s="1" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="721" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A721" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B721" s="1" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C721" t="str">
+        <f>IMCOS("1+i")</f>
+        <v>0,833730025131149-0,988897705762865i</v>
+      </c>
+      <c r="E721" s="1" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="722" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A722" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B722" s="1" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C722" t="str">
+        <f>_xlfn.IMCOSH("4+3i")</f>
+        <v>-27,0349456030742+3,85115333481178i</v>
+      </c>
+      <c r="E722" s="1" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="723" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A723" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B723" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C723" t="str">
+        <f>_xlfn.IMCOT("4+3i")</f>
+        <v>0,00490118239430447-0,999266927805902i</v>
+      </c>
+      <c r="E723" s="1" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="724" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A724" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B724" s="1" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C724" t="str">
+        <f>_xlfn.IMCSC("4+3i")</f>
+        <v>-0,0754898329158637+0,0648774713706355i</v>
+      </c>
+      <c r="E724" s="1" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="725" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A725" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B725" s="1" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C725" t="str">
+        <f>_xlfn.IMCSCH("4+3i")</f>
+        <v>-0,036275889628626-0,0051744731840194i</v>
+      </c>
+      <c r="E725" s="1" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="726" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A726" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B726" s="1" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C726" t="str">
+        <f>IMDIV("-238+240i","10+24i")</f>
+        <v>5+12i</v>
+      </c>
+      <c r="E726" s="1" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="727" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A727" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B727" s="1" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C727" t="str">
+        <f>IMEXP("1+i")</f>
+        <v>1,46869393991589+2,28735528717884i</v>
+      </c>
+      <c r="E727" s="1" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="728" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A728" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B728" s="1" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C728" t="str">
+        <f>IMLN("3+4i")</f>
+        <v>1,6094379124341+0,927295218001612i</v>
+      </c>
+      <c r="E728" s="1" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="729" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A729" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B729" s="1" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C729" t="str">
+        <f>IMLOG10("3+4i")</f>
+        <v>0,698970004336019+0,402719196273373i</v>
+      </c>
+      <c r="E729" s="1" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="730" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A730" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B730" s="1" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C730" t="str">
+        <f>IMLOG2("3+4i")</f>
+        <v>2,32192809488736+1,33780421245098i</v>
+      </c>
+      <c r="E730" s="1" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="731" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A731" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B731" s="1" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C731" t="str">
+        <f>IMPOWER("2+3i",3)</f>
+        <v>-46+9,00000000000001i</v>
+      </c>
+      <c r="E731" s="1" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="732" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A732" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B732" s="1" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C732" t="str">
+        <f>IMPOWER("2+3i",0.5)</f>
+        <v>1,67414922803554+0,895977476129838i</v>
+      </c>
+      <c r="E732" s="1" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="733" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A733" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B733" s="1" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C733" t="str">
+        <f>IMPRODUCT("3+4i","5-3i")</f>
+        <v>27+11i</v>
+      </c>
+      <c r="E733" s="1" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="734" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A734" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B734" s="1" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C734" t="str">
+        <f>IMPRODUCT("1+2i",30)</f>
+        <v>30+60i</v>
+      </c>
+      <c r="E734" s="1" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="735" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A735" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B735" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C735" t="str">
+        <f>_xlfn.IMSEC("4+3i")</f>
+        <v>-0,0652940278579471-0,0752249603027732i</v>
+      </c>
+      <c r="E735" s="1" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="736" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A736" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B736" s="1" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C736" t="str">
+        <f>_xlfn.IMSECH("4+3i")</f>
+        <v>-0,0362534969158689-0,00516434460775318i</v>
+      </c>
+      <c r="E736" s="1" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="737" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A737" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B737" s="1" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C737" t="str">
+        <f>IMSIN("4+3i")</f>
+        <v>-7,61923172032141-6,548120040911i</v>
+      </c>
+      <c r="E737" s="1" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="738" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A738" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B738" s="1" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C738" t="str">
+        <f>_xlfn.IMSINH("4+3i")</f>
+        <v>-27,0168132580039+3,85373803791938i</v>
+      </c>
+      <c r="E738" s="1" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="739" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A739" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B739" s="1" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C739" t="str">
+        <f>IMSQRT("1+i")</f>
+        <v>1,09868411346781+0,455089860562227i</v>
+      </c>
+      <c r="E739" s="1" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="740" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A740" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B740" s="1" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C740" t="str">
+        <f>IMSQRT("-4")</f>
+        <v>1,22514845490862E-16+2i</v>
+      </c>
+      <c r="E740" s="1" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="741" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A741" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B741" s="1" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C741" t="str">
+        <f>IMSUB("13+4i","5+3i")</f>
+        <v>8+i</v>
+      </c>
+      <c r="E741" s="1" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="742" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A742" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B742" s="1" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C742" t="str">
+        <f>IMSUM("3+4i","5-3i")</f>
+        <v>8+i</v>
+      </c>
+      <c r="E742" s="1" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="743" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A743" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B743" s="1" t="s">
+        <v>1530</v>
+      </c>
+      <c r="C743" t="str">
+        <f>IMSUM("1+i","2-i")</f>
+        <v>3</v>
+      </c>
+      <c r="E743" s="1" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="744" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A744" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B744" s="1" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C744" t="str">
+        <f>_xlfn.IMTAN("4+3i")</f>
+        <v>0,00490825806749606+1,00070953606723i</v>
+      </c>
+      <c r="E744" s="1" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="745" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A745" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B745" s="1" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C745">
+        <f>IMABS("1,5+2i")</f>
+        <v>2.5</v>
+      </c>
+      <c r="E745" s="1" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="746" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A746" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B746" s="1" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C746">
+        <f>IMREAL("j")</f>
+        <v>0</v>
+      </c>
+      <c r="E746" s="1" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="747" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A747" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B747" s="1" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C747">
+        <f>BESSELI(1.5,1)</f>
+        <v>0.98166642847516605</v>
+      </c>
+      <c r="E747" s="1" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="748" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A748" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B748" s="1" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C748">
+        <f>BESSELI(2.5,0)</f>
+        <v>3.2898391723912908</v>
+      </c>
+      <c r="E748" s="1" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="749" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A749" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B749" s="1" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C749">
+        <f>BESSELI(4,3)</f>
+        <v>3.3372758428109215</v>
+      </c>
+      <c r="E749" s="1" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="750" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A750" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B750" s="1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C750">
+        <f>BESSELJ(1.9,2)</f>
+        <v>0.3299258286697852</v>
+      </c>
+      <c r="E750" s="1" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="751" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A751" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B751" s="1" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C751">
+        <f>BESSELJ(10,0)</f>
+        <v>-0.24593576444129961</v>
+      </c>
+      <c r="E751" s="1" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="752" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A752" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B752" s="1" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C752">
+        <f>BESSELJ(0.5,1)</f>
+        <v>0.24226845767957006</v>
+      </c>
+      <c r="E752" s="1" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="753" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A753" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B753" s="1" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C753">
+        <f>BESSELJ(15,5)</f>
+        <v>0.13045601477822388</v>
+      </c>
+      <c r="E753" s="1" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="754" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A754" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B754" s="1" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C754">
+        <f>BESSELK(1.5,1)</f>
+        <v>0.27738780363225868</v>
+      </c>
+      <c r="E754" s="1" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="755" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A755" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B755" s="1" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C755">
+        <f>BESSELK(0.5,0)</f>
+        <v>0.9244190350213235</v>
+      </c>
+      <c r="E755" s="1" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="756" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A756" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B756" s="1" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C756">
+        <f>BESSELK(3,4)</f>
+        <v>0.30585121054817827</v>
+      </c>
+      <c r="E756" s="1" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="757" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A757" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B757" s="1" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C757">
+        <f>BESSELY(2.5,1)</f>
+        <v>0.14591813750831284</v>
+      </c>
+      <c r="E757" s="1" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="758" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A758" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B758" s="1" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C758">
+        <f>BESSELY(10,0)</f>
+        <v>5.5671167430951227E-2</v>
+      </c>
+      <c r="E758" s="1" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="759" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A759" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B759" s="1" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C759">
+        <f>BESSELY(1,3)</f>
+        <v>-5.8215176322626707</v>
+      </c>
+      <c r="E759" s="1" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="760" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A760" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B760" s="1" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C760">
+        <f>CONVERT(1,"lbm","kg")</f>
+        <v>0.45359237000000002</v>
+      </c>
+      <c r="E760" s="1" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="761" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A761" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B761" s="1" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C761">
+        <f>CONVERT(68,"F","C")</f>
+        <v>20</v>
+      </c>
+      <c r="E761" s="1" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="762" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A762" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B762" s="1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C762" t="e">
+        <f>CONVERT(2.5,"ft","sec")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E762" s="1" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="763" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A763" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B763" s="1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C763">
+        <f>CONVERT(CONVERT(100,"ft","m"),"ft","m")</f>
+        <v>9.2903040000000008</v>
+      </c>
+      <c r="E763" s="1" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="764" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A764" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B764" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C764">
+        <f>CONVERT(1,"mi","km")</f>
+        <v>1.6093440000000001</v>
+      </c>
+      <c r="E764" s="1" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="765" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A765" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B765" s="1" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C765">
+        <f>CONVERT(10,"in","cm")</f>
+        <v>25.4</v>
+      </c>
+      <c r="E765" s="1" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="766" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A766" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B766" s="1" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C766">
+        <f>CONVERT(1,"yr","day")</f>
+        <v>365.25</v>
+      </c>
+      <c r="E766" s="1" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="767" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A767" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B767" s="1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C767">
+        <f>CONVERT(1,"atm","mmHg")</f>
+        <v>760.00210017851521</v>
+      </c>
+      <c r="E767" s="1" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="768" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A768" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B768" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C768">
+        <f>CONVERT(1,"cal","J")</f>
+        <v>4.1867999999999999</v>
+      </c>
+      <c r="E768" s="1" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="769" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A769" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B769" s="1" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C769">
+        <f>CONVERT(1,"HP","W")</f>
+        <v>745.69987158227025</v>
+      </c>
+      <c r="E769" s="1" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="770" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A770" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B770" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C770">
+        <f>CONVERT(1,"gal","l")</f>
+        <v>3.7854117839999999</v>
+      </c>
+      <c r="E770" s="1" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="771" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A771" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B771" s="1" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C771">
+        <f>CONVERT(1,"uk_gal","l")</f>
+        <v>4.5460900000000004</v>
+      </c>
+      <c r="E771" s="1" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="772" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A772" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B772" s="1" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C772">
+        <f>CONVERT(100,"C","K")</f>
+        <v>373.15</v>
+      </c>
+      <c r="E772" s="1" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="773" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A773" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B773" s="1" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C773">
+        <f>CONVERT(0,"C","Rank")</f>
+        <v>491.66999999999996</v>
+      </c>
+      <c r="E773" s="1" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="774" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A774" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B774" s="1" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C774">
+        <f>CONVERT(1,"kn","m/s")</f>
+        <v>0.51444444444444448</v>
+      </c>
+      <c r="E774" s="1" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="775" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A775" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B775" s="1" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C775">
+        <f>CONVERT(1,"mph","m/s")</f>
+        <v>0.44703999999999999</v>
+      </c>
+      <c r="E775" s="1" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="776" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A776" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B776" s="1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C776">
+        <f>CONVERT(1,"ha","m2")</f>
+        <v>10000</v>
+      </c>
+      <c r="E776" s="1" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="777" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A777" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B777" s="1" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C777">
+        <f>CONVERT(1,"km2","m2")</f>
+        <v>1000000</v>
+      </c>
+      <c r="E777" s="1" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="778" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A778" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B778" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C778">
+        <f>CONVERT(1,"m3","l")</f>
+        <v>1000</v>
+      </c>
+      <c r="E778" s="1" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="779" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A779" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B779" s="1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C779">
+        <f>CONVERT(1,"Gibyte","bit")</f>
+        <v>8589934592</v>
+      </c>
+      <c r="E779" s="1" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="780" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A780" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B780" s="1" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C780">
+        <f>CONVERT(1,"kbyte","byte")</f>
+        <v>1000</v>
+      </c>
+      <c r="E780" s="1" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="781" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A781" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B781" s="1" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C781">
+        <f>CONVERT(1,"BTU","J")</f>
+        <v>1055.05585262</v>
+      </c>
+      <c r="E781" s="1" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="782" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A782" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B782" s="1" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C782">
+        <f>CONVERT(1,"eV","J")</f>
+        <v>1.602176487E-19</v>
+      </c>
+      <c r="E782" s="1" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="783" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A783" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B783" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C783">
+        <f>CONVERT(1,"T","ga")</f>
+        <v>10000</v>
+      </c>
+      <c r="E783" s="1" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="784" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A784" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B784" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C784">
+        <f>CONVERT(1,"stone","kg")</f>
+        <v>6.3502931799999995</v>
+      </c>
+      <c r="E784" s="1" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="785" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A785" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B785" s="1" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C785">
+        <f>CONVERT(1,"ozm","g")</f>
+        <v>28.349523125000001</v>
+      </c>
+      <c r="E785" s="1" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="786" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A786" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B786" s="1" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C786">
+        <f>CONVERT(1,"psi","Pa")</f>
+        <v>6894.7572931683617</v>
+      </c>
+      <c r="E786" s="1" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="787" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A787" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B787" s="1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C787">
+        <f>CONVERT(1,"Nmi","m")</f>
+        <v>1852</v>
+      </c>
+      <c r="E787" s="1" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="788" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A788" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B788" s="1" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C788">
+        <f>CONVERT(1,"ly","m")</f>
+        <v>9460730472580800</v>
+      </c>
+      <c r="E788" s="1" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="789" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A789" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B789" s="1" t="s">
+        <v>1622</v>
+      </c>
+      <c r="C789">
+        <f>CONVERT(1,"cup","tsp")</f>
+        <v>48</v>
+      </c>
+      <c r="E789" s="1" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="790" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A790" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B790" s="1" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C790">
+        <f>CONVERT(1,"lbf","N")</f>
+        <v>4.4482216152605005</v>
+      </c>
+      <c r="E790" s="1" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="791" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A791" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B791" s="1" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C791">
+        <f>CONVERT(1,"Wh","J")</f>
+        <v>3600</v>
+      </c>
+      <c r="E791" s="1" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="792" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A792" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B792" s="1" t="s">
+        <v>1628</v>
+      </c>
+      <c r="C792">
+        <f>CONVERT(1,"mm","ang")</f>
+        <v>10000000</v>
+      </c>
+      <c r="E792" s="1" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="793" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A793" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B793" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C793">
+        <f>CONVERT(1,"ft3","l")</f>
+        <v>28.316846592000001</v>
+      </c>
+      <c r="E793" s="1" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="794" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A794" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B794" s="1" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C794">
+        <f>CONVERT(1,"in2","cm2")</f>
+        <v>6.4516</v>
+      </c>
+      <c r="E794" s="1" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="795" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A795" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B795" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C795">
+        <f>CONVERT(1,"barrel","gal")</f>
+        <v>42.000000000000007</v>
+      </c>
+      <c r="E795" s="1" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="796" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A796" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B796" s="1" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C796">
+        <f>CONVERT(1,"Reau","C")</f>
+        <v>1.25</v>
+      </c>
+      <c r="E796" s="1" t="s">
+        <v>1637</v>
       </c>
     </row>
   </sheetData>

--- a/tests/fixtures/formulas.xlsx
+++ b/tests/fixtures/formulas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\New_Office\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{067A265D-5E88-4507-AD56-FAFAAB4C6990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E969D11C-7405-4A42-BB2F-AEEC21006342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{DD5682B5-DED2-461D-A0CC-D388BB63C15D}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{A0747270-97E6-41F9-9464-99451C548891}"/>
   </bookViews>
   <sheets>
     <sheet name="Данные" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2435" uniqueCount="1638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2660" uniqueCount="1789">
   <si>
     <t>Имя</t>
   </si>
@@ -4978,6 +4978,459 @@
   </si>
   <si>
     <t>=ПРЕОБР(1;"Reau";"C")</t>
+  </si>
+  <si>
+    <t>Пакет D: ценные бумаги и прочие финансовые</t>
+  </si>
+  <si>
+    <t>COUPDAYBS(DATE(2011,1,25),DATE(2011,11,15),2,1)</t>
+  </si>
+  <si>
+    <t>=ДНЕЙКУПОНДО(ДАТА(2011;1;25);ДАТА(2011;11;15);2;1)</t>
+  </si>
+  <si>
+    <t>COUPDAYS(DATE(2011,1,25),DATE(2011,11,15),2,1)</t>
+  </si>
+  <si>
+    <t>=ДНЕЙКУПОН(ДАТА(2011;1;25);ДАТА(2011;11;15);2;1)</t>
+  </si>
+  <si>
+    <t>COUPDAYSNC(DATE(2011,1,25),DATE(2011,11,15),2,1)</t>
+  </si>
+  <si>
+    <t>=ДНЕЙКУПОНПОСЛЕ(ДАТА(2011;1;25);ДАТА(2011;11;15);2;1)</t>
+  </si>
+  <si>
+    <t>COUPNCD(DATE(2011,1,25),DATE(2011,11,15),2,1)</t>
+  </si>
+  <si>
+    <t>=ДАТАКУПОНПОСЛЕ(ДАТА(2011;1;25);ДАТА(2011;11;15);2;1)</t>
+  </si>
+  <si>
+    <t>COUPNUM(DATE(2007,1,25),DATE(2008,11,15),2,1)</t>
+  </si>
+  <si>
+    <t>=ЧИСЛКУПОН(ДАТА(2007;1;25);ДАТА(2008;11;15);2;1)</t>
+  </si>
+  <si>
+    <t>COUPPCD(DATE(2011,1,25),DATE(2011,11,15),2,1)</t>
+  </si>
+  <si>
+    <t>=ДАТАКУПОНДО(ДАТА(2011;1;25);ДАТА(2011;11;15);2;1)</t>
+  </si>
+  <si>
+    <t>COUPDAYBS(DATE(2026,1,15),DATE(2030,6,30),4,0)</t>
+  </si>
+  <si>
+    <t>=ДНЕЙКУПОНДО(ДАТА(2026;1;15);ДАТА(2030;6;30);4;0)</t>
+  </si>
+  <si>
+    <t>COUPDAYS(DATE(2026,1,15),DATE(2030,6,30),4,0)</t>
+  </si>
+  <si>
+    <t>=ДНЕЙКУПОН(ДАТА(2026;1;15);ДАТА(2030;6;30);4;0)</t>
+  </si>
+  <si>
+    <t>COUPDAYSNC(DATE(2026,1,15),DATE(2030,6,30),4,0)</t>
+  </si>
+  <si>
+    <t>=ДНЕЙКУПОНПОСЛЕ(ДАТА(2026;1;15);ДАТА(2030;6;30);4;0)</t>
+  </si>
+  <si>
+    <t>COUPDAYSNC(DATE(2026,3,1),DATE(2030,8,31),2,4)</t>
+  </si>
+  <si>
+    <t>=ДНЕЙКУПОНПОСЛЕ(ДАТА(2026;3;1);ДАТА(2030;8;31);2;4)</t>
+  </si>
+  <si>
+    <t>COUPDAYS(DATE(2026,3,1),DATE(2030,8,31),1,3)</t>
+  </si>
+  <si>
+    <t>=ДНЕЙКУПОН(ДАТА(2026;3;1);ДАТА(2030;8;31);1;3)</t>
+  </si>
+  <si>
+    <t>COUPNCD(DATE(2026,3,1),DATE(2030,8,31),4,0)</t>
+  </si>
+  <si>
+    <t>=ДАТАКУПОНПОСЛЕ(ДАТА(2026;3;1);ДАТА(2030;8;31);4;0)</t>
+  </si>
+  <si>
+    <t>COUPNUM(DATE(2026,3,1),DATE(2030,8,31),4,2)</t>
+  </si>
+  <si>
+    <t>=ЧИСЛКУПОН(ДАТА(2026;3;1);ДАТА(2030;8;31);4;2)</t>
+  </si>
+  <si>
+    <t>PRICE(DATE(2008,2,15),DATE(2017,11,15),0.0575,0.065,100,2,0)</t>
+  </si>
+  <si>
+    <t>=ЦЕНА(ДАТА(2008;2;15);ДАТА(2017;11;15);0,0575;0,065;100;2;0)</t>
+  </si>
+  <si>
+    <t>PRICE(DATE(2026,1,10),DATE(2036,6,30),0.08,0.07,100,1,1)</t>
+  </si>
+  <si>
+    <t>=ЦЕНА(ДАТА(2026;1;10);ДАТА(2036;6;30);0,08;0,07;100;1;1)</t>
+  </si>
+  <si>
+    <t>PRICE(DATE(2026,1,10),DATE(2026,6,30),0.08,0.07,100,4,3)</t>
+  </si>
+  <si>
+    <t>=ЦЕНА(ДАТА(2026;1;10);ДАТА(2026;6;30);0,08;0,07;100;4;3)</t>
+  </si>
+  <si>
+    <t>YIELD(DATE(2008,2,15),DATE(2016,11,15),0.0575,95.04287,100,2,0)</t>
+  </si>
+  <si>
+    <t>=ДОХОД(ДАТА(2008;2;15);ДАТА(2016;11;15);0,0575;95,04287;100;2;0)</t>
+  </si>
+  <si>
+    <t>YIELD(DATE(2026,1,10),DATE(2026,6,30),0.08,99.5,100,4,1)</t>
+  </si>
+  <si>
+    <t>=ДОХОД(ДАТА(2026;1;10);ДАТА(2026;6;30);0,08;99,5;100;4;1)</t>
+  </si>
+  <si>
+    <t>DURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,0.09,2,1)</t>
+  </si>
+  <si>
+    <t>=ДЛИТ(ДАТА(2018;7;1);ДАТА(2048;1;1);0,08;0,09;2;1)</t>
+  </si>
+  <si>
+    <t>MDURATION(DATE(2008,1,1),DATE(2016,1,1),0.08,0.09,2,1)</t>
+  </si>
+  <si>
+    <t>=МДЛИТ(ДАТА(2008;1;1);ДАТА(2016;1;1);0,08;0,09;2;1)</t>
+  </si>
+  <si>
+    <t>ACCRINT(DATE(2008,3,1),DATE(2008,8,31),DATE(2008,5,1),0.1,1000,2,0)</t>
+  </si>
+  <si>
+    <t>=НАКОПДОХОД(ДАТА(2008;3;1);ДАТА(2008;8;31);ДАТА(2008;5;1);0,1;1000;2;0)</t>
+  </si>
+  <si>
+    <t>ACCRINT(DATE(2008,3,5),DATE(2008,8,31),DATE(2008,5,1),0.1,1000,2,0,FALSE)</t>
+  </si>
+  <si>
+    <t>=НАКОПДОХОД(ДАТА(2008;3;5);ДАТА(2008;8;31);ДАТА(2008;5;1);0,1;1000;2;0;ЛОЖЬ)</t>
+  </si>
+  <si>
+    <t>ACCRINTM(DATE(2008,4,1),DATE(2008,6,15),0.1,1000,3)</t>
+  </si>
+  <si>
+    <t>=НАКОПДОХОДПОГАШ(ДАТА(2008;4;1);ДАТА(2008;6;15);0,1;1000;3)</t>
+  </si>
+  <si>
+    <t>DISC(DATE(2018,7,1),DATE(2048,1,1),97.975,100,1)</t>
+  </si>
+  <si>
+    <t>=СКИДКА(ДАТА(2018;7;1);ДАТА(2048;1;1);97,975;100;1)</t>
+  </si>
+  <si>
+    <t>INTRATE(DATE(2008,2,15),DATE(2008,5,15),1000000,1014420,2)</t>
+  </si>
+  <si>
+    <t>=ИНОРМА(ДАТА(2008;2;15);ДАТА(2008;5;15);1000000;1014420;2)</t>
+  </si>
+  <si>
+    <t>RECEIVED(DATE(2008,2,15),DATE(2008,5,15),1000000,0.0575,2)</t>
+  </si>
+  <si>
+    <t>=ПОЛУЧЕНО(ДАТА(2008;2;15);ДАТА(2008;5;15);1000000;0,0575;2)</t>
+  </si>
+  <si>
+    <t>PRICEDISC(DATE(2008,2,16),DATE(2008,3,1),0.0525,100,2)</t>
+  </si>
+  <si>
+    <t>=ЦЕНАСКИДКА(ДАТА(2008;2;16);ДАТА(2008;3;1);0,0525;100;2)</t>
+  </si>
+  <si>
+    <t>YIELDDISC(DATE(2008,2,16),DATE(2008,3,1),99.795,100,2)</t>
+  </si>
+  <si>
+    <t>=ДОХОДСКИДКА(ДАТА(2008;2;16);ДАТА(2008;3;1);99,795;100;2)</t>
+  </si>
+  <si>
+    <t>PRICEMAT(DATE(2008,2,15),DATE(2008,4,13),DATE(2007,11,11),0.061,0.061,0)</t>
+  </si>
+  <si>
+    <t>=ЦЕНАПОГАШ(ДАТА(2008;2;15);ДАТА(2008;4;13);ДАТА(2007;11;11);0,061;0,061;0)</t>
+  </si>
+  <si>
+    <t>YIELDMAT(DATE(2008,3,15),DATE(2008,11,3),DATE(2007,11,8),0.0625,100.0123,0)</t>
+  </si>
+  <si>
+    <t>=ДОХОДПОГАШ(ДАТА(2008;3;15);ДАТА(2008;11;3);ДАТА(2007;11;8);0,0625;100,0123;0)</t>
+  </si>
+  <si>
+    <t>TBILLEQ(DATE(2008,3,31),DATE(2008,6,1),0.0914)</t>
+  </si>
+  <si>
+    <t>=РАВНОКЧЕК(ДАТА(2008;3;31);ДАТА(2008;6;1);0,0914)</t>
+  </si>
+  <si>
+    <t>TBILLEQ(DATE(2008,1,1),DATE(2008,10,1),0.05)</t>
+  </si>
+  <si>
+    <t>=РАВНОКЧЕК(ДАТА(2008;1;1);ДАТА(2008;10;1);0,05)</t>
+  </si>
+  <si>
+    <t>TBILLPRICE(DATE(2008,3,31),DATE(2008,6,1),0.09)</t>
+  </si>
+  <si>
+    <t>=ЦЕНАКЧЕК(ДАТА(2008;3;31);ДАТА(2008;6;1);0,09)</t>
+  </si>
+  <si>
+    <t>TBILLYIELD(DATE(2008,3,31),DATE(2008,6,1),98.45)</t>
+  </si>
+  <si>
+    <t>=ДОХОДКЧЕК(ДАТА(2008;3;31);ДАТА(2008;6;1);98,45)</t>
+  </si>
+  <si>
+    <t>ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),0.0375,0.0405,100,2,0)</t>
+  </si>
+  <si>
+    <t>=ЦЕНАПОСЛНЕРЕГ(ДАТА(2008;2;7);ДАТА(2008;6;15);ДАТА(2007;10;15);0,0375;0,0405;100;2;0)</t>
+  </si>
+  <si>
+    <t>ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),0.0375,99.875,100,2,0)</t>
+  </si>
+  <si>
+    <t>=ДОХОДПОСЛНЕРЕГ(ДАТА(2008;4;20);ДАТА(2008;6;15);ДАТА(2007;12;24);0,0375;99,875;100;2;0)</t>
+  </si>
+  <si>
+    <t>ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,100,2,1)</t>
+  </si>
+  <si>
+    <t>=ЦЕНАПЕРВНЕРЕГ(ДАТА(2008;11;11);ДАТА(2021;3;1);ДАТА(2008;10;15);ДАТА(2009;3;1);0,0785;0,0625;100;2;1)</t>
+  </si>
+  <si>
+    <t>ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,100,2,0)</t>
+  </si>
+  <si>
+    <t>=ДОХОДПЕРВНЕРЕГ(ДАТА(2008;11;11);ДАТА(2021;3;1);ДАТА(2008;10;15);ДАТА(2009;3;1);0,0575;84,5;100;2;0)</t>
+  </si>
+  <si>
+    <t>CUMIPMT(0.09/12,360,125000,13,24,0)</t>
+  </si>
+  <si>
+    <t>=ОБЩПЛАТ(0,09/12;360;125000;13;24;0)</t>
+  </si>
+  <si>
+    <t>CUMIPMT(0.09/12,360,125000,1,1,0)</t>
+  </si>
+  <si>
+    <t>=ОБЩПЛАТ(0,09/12;360;125000;1;1;0)</t>
+  </si>
+  <si>
+    <t>CUMPRINC(0.09/12,360,125000,13,24,0)</t>
+  </si>
+  <si>
+    <t>=ОБЩДОХОД(0,09/12;360;125000;13;24;0)</t>
+  </si>
+  <si>
+    <t>CUMPRINC(0.09/12,360,125000,1,1,1)</t>
+  </si>
+  <si>
+    <t>=ОБЩДОХОД(0,09/12;360;125000;1;1;1)</t>
+  </si>
+  <si>
+    <t>DOLLARDE(1.02,16)</t>
+  </si>
+  <si>
+    <t>=РУБЛЬ.ДЕС(1,02;16)</t>
+  </si>
+  <si>
+    <t>DOLLARDE(1.1,32)</t>
+  </si>
+  <si>
+    <t>=РУБЛЬ.ДЕС(1,1;32)</t>
+  </si>
+  <si>
+    <t>DOLLARFR(1.125,16)</t>
+  </si>
+  <si>
+    <t>=РУБЛЬ.ДРОБЬ(1,125;16)</t>
+  </si>
+  <si>
+    <t>DOLLARFR(1.125,32)</t>
+  </si>
+  <si>
+    <t>=РУБЛЬ.ДРОБЬ(1,125;32)</t>
+  </si>
+  <si>
+    <t>FVSCHEDULE(1,{0.09,0.11,0.1})</t>
+  </si>
+  <si>
+    <t>=БЗРАСПИС(1;{0,09;0,11;0,1})</t>
+  </si>
+  <si>
+    <t>ISPMT(0.1/12,1,36,8000000)</t>
+  </si>
+  <si>
+    <t>=ПРОЦПЛАТ(0,1/12;1;36;8000000)</t>
+  </si>
+  <si>
+    <t>MIRR({-120000,39000,30000,21000,37000,46000},0.1,0.12)</t>
+  </si>
+  <si>
+    <t>=МВСД({-120000;39000;30000;21000;37000;46000};0,1;0,12)</t>
+  </si>
+  <si>
+    <t>MIRR({-120000,39000,30000,21000},0.1,0.12)</t>
+  </si>
+  <si>
+    <t>=МВСД({-120000;39000;30000;21000};0,1;0,12)</t>
+  </si>
+  <si>
+    <t>PDURATION(0.025,2000,2200)</t>
+  </si>
+  <si>
+    <t>=ПДЛИТ(0,025;2000;2200)</t>
+  </si>
+  <si>
+    <t>RRI(96,10000,11000)</t>
+  </si>
+  <si>
+    <t>=ЭКВ.СТАВКА(96;10000;11000)</t>
+  </si>
+  <si>
+    <t>VDB(2400,300,10*365,0,1)</t>
+  </si>
+  <si>
+    <t>=ПУО(2400;300;10*365;0;1)</t>
+  </si>
+  <si>
+    <t>VDB(2400,300,10*12,0,1)</t>
+  </si>
+  <si>
+    <t>=ПУО(2400;300;10*12;0;1)</t>
+  </si>
+  <si>
+    <t>VDB(2400,300,10,0,1)</t>
+  </si>
+  <si>
+    <t>=ПУО(2400;300;10;0;1)</t>
+  </si>
+  <si>
+    <t>VDB(2400,300,10*12,6,18)</t>
+  </si>
+  <si>
+    <t>=ПУО(2400;300;10*12;6;18)</t>
+  </si>
+  <si>
+    <t>VDB(2400,300,10*12,6,18,1.5)</t>
+  </si>
+  <si>
+    <t>=ПУО(2400;300;10*12;6;18;1,5)</t>
+  </si>
+  <si>
+    <t>VDB(2400,300,10,0,0.875,1.5)</t>
+  </si>
+  <si>
+    <t>=ПУО(2400;300;10;0;0,875;1,5)</t>
+  </si>
+  <si>
+    <t>VDB(2400,300,10,3,5,2,TRUE)</t>
+  </si>
+  <si>
+    <t>=ПУО(2400;300;10;3;5;2;ИСТИНА)</t>
+  </si>
+  <si>
+    <t>VDB(2400,300,10,1.5,4)</t>
+  </si>
+  <si>
+    <t>=ПУО(2400;300;10;1,5;4)</t>
+  </si>
+  <si>
+    <t>AMORDEGRC(2400,DATE(2008,8,19),DATE(2008,12,31),300,1,0.15,1)</t>
+  </si>
+  <si>
+    <t>=АМОРУМ(2400;ДАТА(2008;8;19);ДАТА(2008;12;31);300;1;0,15;1)</t>
+  </si>
+  <si>
+    <t>AMORDEGRC(2400,DATE(2008,8,19),DATE(2008,12,31),300,0,0.15,1)</t>
+  </si>
+  <si>
+    <t>=АМОРУМ(2400;ДАТА(2008;8;19);ДАТА(2008;12;31);300;0;0,15;1)</t>
+  </si>
+  <si>
+    <t>AMORDEGRC(2400,DATE(2008,8,19),DATE(2008,12,31),300,4,0.15,1)</t>
+  </si>
+  <si>
+    <t>=АМОРУМ(2400;ДАТА(2008;8;19);ДАТА(2008;12;31);300;4;0,15;1)</t>
+  </si>
+  <si>
+    <t>AMORLINC(2400,DATE(2008,8,19),DATE(2008,12,31),300,1,0.15,1)</t>
+  </si>
+  <si>
+    <t>=АМОРУВ(2400;ДАТА(2008;8;19);ДАТА(2008;12;31);300;1;0,15;1)</t>
+  </si>
+  <si>
+    <t>AMORLINC(2400,DATE(2008,8,19),DATE(2008,12,31),300,0,0.15,1)</t>
+  </si>
+  <si>
+    <t>=АМОРУВ(2400;ДАТА(2008;8;19);ДАТА(2008;12;31);300;0;0,15;1)</t>
+  </si>
+  <si>
+    <t>AMORLINC(2400,DATE(2008,8,19),DATE(2008,12,31),300,6,0.15,1)</t>
+  </si>
+  <si>
+    <t>=АМОРУВ(2400;ДАТА(2008;8;19);ДАТА(2008;12;31);300;6;0,15;1)</t>
+  </si>
+  <si>
+    <t>VDB(2400,300,10,0.5,1)</t>
+  </si>
+  <si>
+    <t>=ПУО(2400;300;10;0,5;1)</t>
+  </si>
+  <si>
+    <t>VDB(2400,300,10,0.5,2)</t>
+  </si>
+  <si>
+    <t>=ПУО(2400;300;10;0,5;2)</t>
+  </si>
+  <si>
+    <t>VDB(2400,300,10,1.5,2)</t>
+  </si>
+  <si>
+    <t>=ПУО(2400;300;10;1,5;2)</t>
+  </si>
+  <si>
+    <t>VDB(2400,300,10,1.25,2)</t>
+  </si>
+  <si>
+    <t>=ПУО(2400;300;10;1,25;2)</t>
+  </si>
+  <si>
+    <t>VDB(2400,300,10,2.5,3)</t>
+  </si>
+  <si>
+    <t>=ПУО(2400;300;10;2,5;3)</t>
+  </si>
+  <si>
+    <t>VDB(1000,0,5,0.5,1,1)</t>
+  </si>
+  <si>
+    <t>=ПУО(1000;0;5;0,5;1;1)</t>
+  </si>
+  <si>
+    <t>ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,1,15),DATE(2009,3,1),0.0785,0.0625,100,2,0)</t>
+  </si>
+  <si>
+    <t>=ЦЕНАПЕРВНЕРЕГ(ДАТА(2008;11;11);ДАТА(2021;3;1);ДАТА(2008;1;15);ДАТА(2009;3;1);0,0785;0,0625;100;2;0)</t>
+  </si>
+  <si>
+    <t>ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,1,15),DATE(2009,3,1),0.0785,0.0625,100,2,1)</t>
+  </si>
+  <si>
+    <t>=ЦЕНАПЕРВНЕРЕГ(ДАТА(2008;11;11);ДАТА(2021;3;1);ДАТА(2008;1;15);ДАТА(2009;3;1);0,0785;0,0625;100;2;1)</t>
+  </si>
+  <si>
+    <t>ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,1,15),DATE(2009,3,1),0.0575,84.5,100,2,0)</t>
+  </si>
+  <si>
+    <t>=ДОХОДПЕРВНЕРЕГ(ДАТА(2008;11;11);ДАТА(2021;3;1);ДАТА(2008;1;15);ДАТА(2009;3;1);0,0575;84,5;100;2;0)</t>
   </si>
 </sst>
 </file>
@@ -5364,7 +5817,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0321EED-90EB-4541-8CEC-C44EE68CE245}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{830D47FE-8185-4B59-A512-4E3A80BCEE48}">
   <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5683,7 +6136,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC03273A-1695-4B7E-8AC4-41592AABC62C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AB41647-A169-48EA-8DE9-E5299ADD36A6}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5703,7 +6156,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537813D3-AD55-4462-B438-7027C06FC366}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACDE9390-DE20-45EF-975C-E361FFC7E761}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5723,7 +6176,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A70D965B-F6C3-408F-9473-14306BF4ECF4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33480E4-B5A1-4535-A399-08D18DBA5B5A}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5743,8 +6196,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{435AC6E0-2581-4D1E-A765-BE261653750C}">
-  <dimension ref="A1:E796"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8207E4-129D-4D3E-AE88-33112011EF0B}">
+  <dimension ref="A1:E871"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.140625" style="1"/>
@@ -11106,7 +11559,7 @@
       </c>
       <c r="C358" s="7">
         <f ca="1">NOW()</f>
-        <v>46305.833494560182</v>
+        <v>46305.83841365741</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>757</v>
@@ -11121,7 +11574,7 @@
       </c>
       <c r="C359">
         <f ca="1">RAND()</f>
-        <v>0.70047170638689604</v>
+        <v>0.24388080380197363</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>759</v>
@@ -11136,7 +11589,7 @@
       </c>
       <c r="C360">
         <f ca="1">RANDBETWEEN(1,10)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>761</v>
@@ -17680,6 +18133,1131 @@
       </c>
       <c r="E796" s="1" t="s">
         <v>1637</v>
+      </c>
+    </row>
+    <row r="797" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A797" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B797" s="1" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C797">
+        <f>COUPDAYBS(DATE(2011,1,25),DATE(2011,11,15),2,1)</f>
+        <v>71</v>
+      </c>
+      <c r="E797" s="1" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="798" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A798" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B798" s="1" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C798">
+        <f>COUPDAYS(DATE(2011,1,25),DATE(2011,11,15),2,1)</f>
+        <v>181</v>
+      </c>
+      <c r="E798" s="1" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="799" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A799" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B799" s="1" t="s">
+        <v>1643</v>
+      </c>
+      <c r="C799">
+        <f>COUPDAYSNC(DATE(2011,1,25),DATE(2011,11,15),2,1)</f>
+        <v>110</v>
+      </c>
+      <c r="E799" s="1" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="800" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A800" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B800" s="1" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C800">
+        <f>COUPNCD(DATE(2011,1,25),DATE(2011,11,15),2,1)</f>
+        <v>40678</v>
+      </c>
+      <c r="E800" s="1" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="801" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A801" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B801" s="1" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C801">
+        <f>COUPNUM(DATE(2007,1,25),DATE(2008,11,15),2,1)</f>
+        <v>4</v>
+      </c>
+      <c r="E801" s="1" t="s">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="802" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A802" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B802" s="1" t="s">
+        <v>1649</v>
+      </c>
+      <c r="C802">
+        <f>COUPPCD(DATE(2011,1,25),DATE(2011,11,15),2,1)</f>
+        <v>40497</v>
+      </c>
+      <c r="E802" s="1" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="803" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A803" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B803" s="1" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C803">
+        <f>COUPDAYBS(DATE(2026,1,15),DATE(2030,6,30),4,0)</f>
+        <v>15</v>
+      </c>
+      <c r="E803" s="1" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="804" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A804" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B804" s="1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C804">
+        <f>COUPDAYS(DATE(2026,1,15),DATE(2030,6,30),4,0)</f>
+        <v>90</v>
+      </c>
+      <c r="E804" s="1" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="805" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A805" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B805" s="1" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C805">
+        <f>COUPDAYSNC(DATE(2026,1,15),DATE(2030,6,30),4,0)</f>
+        <v>75</v>
+      </c>
+      <c r="E805" s="1" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="806" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A806" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B806" s="1" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C806">
+        <f>COUPDAYSNC(DATE(2026,3,1),DATE(2030,8,31),2,4)</f>
+        <v>179</v>
+      </c>
+      <c r="E806" s="1" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="807" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A807" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B807" s="1" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C807">
+        <f>COUPDAYS(DATE(2026,3,1),DATE(2030,8,31),1,3)</f>
+        <v>365</v>
+      </c>
+      <c r="E807" s="1" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="808" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A808" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B808" s="1" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C808">
+        <f>COUPNCD(DATE(2026,3,1),DATE(2030,8,31),4,0)</f>
+        <v>46173</v>
+      </c>
+      <c r="E808" s="1" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="809" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A809" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B809" s="1" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C809">
+        <f>COUPNUM(DATE(2026,3,1),DATE(2030,8,31),4,2)</f>
+        <v>18</v>
+      </c>
+      <c r="E809" s="1" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="810" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A810" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B810" s="1" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C810">
+        <f>PRICE(DATE(2008,2,15),DATE(2017,11,15),0.0575,0.065,100,2,0)</f>
+        <v>94.634361621322128</v>
+      </c>
+      <c r="E810" s="1" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="811" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A811" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B811" s="1" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C811">
+        <f>PRICE(DATE(2026,1,10),DATE(2036,6,30),0.08,0.07,100,1,1)</f>
+        <v>107.18273231504094</v>
+      </c>
+      <c r="E811" s="1" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="812" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A812" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B812" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C812">
+        <f>PRICE(DATE(2026,1,10),DATE(2026,6,30),0.08,0.07,100,4,3)</f>
+        <v>100.45922662459751</v>
+      </c>
+      <c r="E812" s="1" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="813" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A813" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B813" s="1" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C813">
+        <f>YIELD(DATE(2008,2,15),DATE(2016,11,15),0.0575,95.04287,100,2,0)</f>
+        <v>6.5000006880731431E-2</v>
+      </c>
+      <c r="E813" s="1" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="814" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A814" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B814" s="1" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C814">
+        <f>YIELD(DATE(2026,1,10),DATE(2026,6,30),0.08,99.5,100,4,1)</f>
+        <v>9.08885094704866E-2</v>
+      </c>
+      <c r="E814" s="1" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="815" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A815" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B815" s="1" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C815">
+        <f>DURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,0.09,2,1)</f>
+        <v>10.919145281591932</v>
+      </c>
+      <c r="E815" s="1" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="816" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A816" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B816" s="1" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C816">
+        <f>MDURATION(DATE(2008,1,1),DATE(2016,1,1),0.08,0.09,2,1)</f>
+        <v>5.7356698139188387</v>
+      </c>
+      <c r="E816" s="1" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="817" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A817" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B817" s="1" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C817">
+        <f>ACCRINT(DATE(2008,3,1),DATE(2008,8,31),DATE(2008,5,1),0.1,1000,2,0)</f>
+        <v>16.666666666666664</v>
+      </c>
+      <c r="E817" s="1" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="818" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A818" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B818" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C818">
+        <f>ACCRINT(DATE(2008,3,5),DATE(2008,8,31),DATE(2008,5,1),0.1,1000,2,0,FALSE)</f>
+        <v>15.555555555555555</v>
+      </c>
+      <c r="E818" s="1" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="819" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A819" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B819" s="1" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C819">
+        <f>ACCRINTM(DATE(2008,4,1),DATE(2008,6,15),0.1,1000,3)</f>
+        <v>20.547945205479451</v>
+      </c>
+      <c r="E819" s="1" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="820" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A820" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B820" s="1" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C820">
+        <f>DISC(DATE(2018,7,1),DATE(2048,1,1),97.975,100,1)</f>
+        <v>6.8638416912134839E-4</v>
+      </c>
+      <c r="E820" s="1" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="821" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A821" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B821" s="1" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C821">
+        <f>INTRATE(DATE(2008,2,15),DATE(2008,5,15),1000000,1014420,2)</f>
+        <v>5.7680000000000002E-2</v>
+      </c>
+      <c r="E821" s="1" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="822" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A822" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B822" s="1" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C822">
+        <f>RECEIVED(DATE(2008,2,15),DATE(2008,5,15),1000000,0.0575,2)</f>
+        <v>1014584.6544071021</v>
+      </c>
+      <c r="E822" s="1" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="823" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A823" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B823" s="1" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C823">
+        <f>PRICEDISC(DATE(2008,2,16),DATE(2008,3,1),0.0525,100,2)</f>
+        <v>99.795833333333334</v>
+      </c>
+      <c r="E823" s="1" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="824" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A824" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B824" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C824">
+        <f>YIELDDISC(DATE(2008,2,16),DATE(2008,3,1),99.795,100,2)</f>
+        <v>5.2822571986858337E-2</v>
+      </c>
+      <c r="E824" s="1" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="825" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A825" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B825" s="1" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C825">
+        <f>PRICEMAT(DATE(2008,2,15),DATE(2008,4,13),DATE(2007,11,11),0.061,0.061,0)</f>
+        <v>99.984498875556937</v>
+      </c>
+      <c r="E825" s="1" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="826" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A826" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B826" s="1" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C826">
+        <f>YIELDMAT(DATE(2008,3,15),DATE(2008,11,3),DATE(2007,11,8),0.0625,100.0123,0)</f>
+        <v>6.0954333691538673E-2</v>
+      </c>
+      <c r="E826" s="1" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="827" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A827" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B827" s="1" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C827">
+        <f>TBILLEQ(DATE(2008,3,31),DATE(2008,6,1),0.0914)</f>
+        <v>9.4151493565943017E-2</v>
+      </c>
+      <c r="E827" s="1" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="828" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A828" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B828" s="1" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C828">
+        <f>TBILLEQ(DATE(2008,1,1),DATE(2008,10,1),0.05)</f>
+        <v>5.2244231049341214E-2</v>
+      </c>
+      <c r="E828" s="1" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="829" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A829" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B829" s="1" t="s">
+        <v>1703</v>
+      </c>
+      <c r="C829">
+        <f>TBILLPRICE(DATE(2008,3,31),DATE(2008,6,1),0.09)</f>
+        <v>98.45</v>
+      </c>
+      <c r="E829" s="1" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="830" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A830" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B830" s="1" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C830">
+        <f>TBILLYIELD(DATE(2008,3,31),DATE(2008,6,1),98.45)</f>
+        <v>9.141696292534264E-2</v>
+      </c>
+      <c r="E830" s="1" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="831" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A831" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B831" s="1" t="s">
+        <v>1707</v>
+      </c>
+      <c r="C831">
+        <f>ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),0.0375,0.0405,100,2,0)</f>
+        <v>99.87828601472134</v>
+      </c>
+      <c r="E831" s="1" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="832" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A832" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B832" s="1" t="s">
+        <v>1709</v>
+      </c>
+      <c r="C832">
+        <f>ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),0.0375,99.875,100,2,0)</f>
+        <v>4.5192235629169158E-2</v>
+      </c>
+      <c r="E832" s="1" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="833" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A833" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B833" s="1" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C833">
+        <f>ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,100,2,1)</f>
+        <v>113.59771747407883</v>
+      </c>
+      <c r="E833" s="1" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="834" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A834" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B834" s="1" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C834">
+        <f>ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,100,2,0)</f>
+        <v>7.7245541597298878E-2</v>
+      </c>
+      <c r="E834" s="1" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="835" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A835" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B835" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="C835">
+        <f>CUMIPMT(0.09/12,360,125000,13,24,0)</f>
+        <v>-11135.232130750841</v>
+      </c>
+      <c r="E835" s="1" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="836" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A836" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B836" s="1" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C836">
+        <f>CUMIPMT(0.09/12,360,125000,1,1,0)</f>
+        <v>-937.49999999999977</v>
+      </c>
+      <c r="E836" s="1" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="837" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A837" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B837" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C837">
+        <f>CUMPRINC(0.09/12,360,125000,13,24,0)</f>
+        <v>-934.10712342089789</v>
+      </c>
+      <c r="E837" s="1" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="838" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A838" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B838" s="1" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C838">
+        <f>CUMPRINC(0.09/12,360,125000,1,1,1)</f>
+        <v>-998.29108802082203</v>
+      </c>
+      <c r="E838" s="1" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="839" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A839" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B839" s="1" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C839">
+        <f>DOLLARDE(1.02,16)</f>
+        <v>1.125</v>
+      </c>
+      <c r="E839" s="1" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="840" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A840" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B840" s="1" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C840">
+        <f>DOLLARDE(1.1,32)</f>
+        <v>1.3125000000000002</v>
+      </c>
+      <c r="E840" s="1" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="841" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A841" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B841" s="1" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C841">
+        <f>DOLLARFR(1.125,16)</f>
+        <v>1.02</v>
+      </c>
+      <c r="E841" s="1" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="842" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A842" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B842" s="1" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C842">
+        <f>DOLLARFR(1.125,32)</f>
+        <v>1.04</v>
+      </c>
+      <c r="E842" s="1" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="843" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A843" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B843" s="1" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C843">
+        <f>FVSCHEDULE(1,{0.09,0.11,0.1})</f>
+        <v>1.3308900000000004</v>
+      </c>
+      <c r="E843" s="1" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="844" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A844" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B844" s="1" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C844">
+        <f>ISPMT(0.1/12,1,36,8000000)</f>
+        <v>-64814.814814814818</v>
+      </c>
+      <c r="E844" s="1" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="845" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A845" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B845" s="1" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C845" s="6">
+        <f>MIRR({-120000,39000,30000,21000,37000,46000},0.1,0.12)</f>
+        <v>0.12609413036590511</v>
+      </c>
+      <c r="E845" s="1" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="846" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A846" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B846" s="1" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C846" s="6">
+        <f>MIRR({-120000,39000,30000,21000},0.1,0.12)</f>
+        <v>-4.8044655249980806E-2</v>
+      </c>
+      <c r="E846" s="1" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="847" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A847" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B847" s="1" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C847">
+        <f>_xlfn.PDURATION(0.025,2000,2200)</f>
+        <v>3.8598661626226551</v>
+      </c>
+      <c r="E847" s="1" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="848" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A848" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B848" s="1" t="s">
+        <v>1741</v>
+      </c>
+      <c r="C848">
+        <f>_xlfn.RRI(96,10000,11000)</f>
+        <v>9.9330737629133026E-4</v>
+      </c>
+      <c r="E848" s="1" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="849" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A849" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B849" s="1" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C849" s="5">
+        <f>VDB(2400,300,10*365,0,1)</f>
+        <v>1.3150684931506849</v>
+      </c>
+      <c r="E849" s="1" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="850" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A850" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B850" s="1" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C850" s="5">
+        <f>VDB(2400,300,10*12,0,1)</f>
+        <v>40</v>
+      </c>
+      <c r="E850" s="1" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="851" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A851" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B851" s="1" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C851" s="5">
+        <f>VDB(2400,300,10,0,1)</f>
+        <v>480</v>
+      </c>
+      <c r="E851" s="1" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="852" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A852" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B852" s="1" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C852" s="5">
+        <f>VDB(2400,300,10*12,6,18)</f>
+        <v>396.30605326475086</v>
+      </c>
+      <c r="E852" s="1" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="853" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A853" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B853" s="1" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C853" s="5">
+        <f>VDB(2400,300,10*12,6,18,1.5)</f>
+        <v>311.80893665823413</v>
+      </c>
+      <c r="E853" s="1" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="854" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A854" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B854" s="1" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C854" s="5">
+        <f>VDB(2400,300,10,0,0.875,1.5)</f>
+        <v>315</v>
+      </c>
+      <c r="E854" s="1" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="855" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A855" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B855" s="1" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C855" s="5">
+        <f>VDB(2400,300,10,3,5,2,TRUE)</f>
+        <v>442.36800000000017</v>
+      </c>
+      <c r="E855" s="1" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="856" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A856" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B856" s="1" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C856" s="5">
+        <f>VDB(2400,300,10,1.5,4)</f>
+        <v>732.67200000000003</v>
+      </c>
+      <c r="E856" s="1" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="857" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A857" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B857" s="1" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C857">
+        <f>AMORDEGRC(2400,DATE(2008,8,19),DATE(2008,12,31),300,1,0.15,1)</f>
+        <v>776</v>
+      </c>
+      <c r="E857" s="1" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="858" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A858" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B858" s="1" t="s">
+        <v>1761</v>
+      </c>
+      <c r="C858">
+        <f>AMORDEGRC(2400,DATE(2008,8,19),DATE(2008,12,31),300,0,0.15,1)</f>
+        <v>330</v>
+      </c>
+      <c r="E858" s="1" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="859" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A859" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B859" s="1" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C859">
+        <f>AMORDEGRC(2400,DATE(2008,8,19),DATE(2008,12,31),300,4,0.15,1)</f>
+        <v>190</v>
+      </c>
+      <c r="E859" s="1" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="860" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A860" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B860" s="1" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C860">
+        <f>AMORLINC(2400,DATE(2008,8,19),DATE(2008,12,31),300,1,0.15,1)</f>
+        <v>360</v>
+      </c>
+      <c r="E860" s="1" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="861" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A861" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B861" s="1" t="s">
+        <v>1767</v>
+      </c>
+      <c r="C861">
+        <f>AMORLINC(2400,DATE(2008,8,19),DATE(2008,12,31),300,0,0.15,1)</f>
+        <v>131.80327868852461</v>
+      </c>
+      <c r="E861" s="1" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="862" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A862" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B862" s="1" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C862">
+        <f>AMORLINC(2400,DATE(2008,8,19),DATE(2008,12,31),300,6,0.15,1)</f>
+        <v>168.19672131147536</v>
+      </c>
+      <c r="E862" s="1" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="863" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A863" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B863" s="1" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C863" s="5">
+        <f>VDB(2400,300,10,0.5,1)</f>
+        <v>216</v>
+      </c>
+      <c r="E863" s="1" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="864" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A864" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B864" s="1" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C864" s="5">
+        <f>VDB(2400,300,10,0.5,2)</f>
+        <v>604.79999999999995</v>
+      </c>
+      <c r="E864" s="1" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="865" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A865" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B865" s="1" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C865" s="5">
+        <f>VDB(2400,300,10,1.5,2)</f>
+        <v>172.8</v>
+      </c>
+      <c r="E865" s="1" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="866" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A866" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B866" s="1" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C866" s="5">
+        <f>VDB(2400,300,10,1.25,2)</f>
+        <v>273.60000000000002</v>
+      </c>
+      <c r="E866" s="1" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="867" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A867" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B867" s="1" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C867" s="5">
+        <f>VDB(2400,300,10,2.5,3)</f>
+        <v>138.24</v>
+      </c>
+      <c r="E867" s="1" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="868" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A868" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B868" s="1" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C868" s="5">
+        <f>VDB(1000,0,5,0.5,1,1)</f>
+        <v>100</v>
+      </c>
+      <c r="E868" s="1" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="869" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A869" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B869" s="1" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C869">
+        <f>ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,1,15),DATE(2009,3,1),0.0785,0.0625,100,2,0)</f>
+        <v>113.48952645174103</v>
+      </c>
+      <c r="E869" s="1" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="870" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A870" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B870" s="1" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C870">
+        <f>ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,1,15),DATE(2009,3,1),0.0785,0.0625,100,2,1)</f>
+        <v>113.48894083961049</v>
+      </c>
+      <c r="E870" s="1" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="871" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A871" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B871" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C871">
+        <f>ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,1,15),DATE(2009,3,1),0.0575,84.5,100,2,0)</f>
+        <v>7.7105580281663713E-2</v>
+      </c>
+      <c r="E871" s="1" t="s">
+        <v>1788</v>
       </c>
     </row>
   </sheetData>
